--- a/src/attributions/attributions_saliency_traj_199.xlsx
+++ b/src/attributions/attributions_saliency_traj_199.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG16"/>
+  <dimension ref="A1:GG14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1568,571 +1568,571 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.0157480463385582</v>
+        <v>0.1236418411135674</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6667063236236572</v>
+        <v>1.193600177764893</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04024368897080421</v>
+        <v>0.01858645677566528</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1303372979164124</v>
+        <v>0.1548881083726883</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1456082314252853</v>
+        <v>0.3246920108795166</v>
       </c>
       <c r="F3" t="n">
-        <v>0.416893869638443</v>
+        <v>1.097209334373474</v>
       </c>
       <c r="G3" t="n">
-        <v>0.06967772543430328</v>
+        <v>0.2354249209165573</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09963512420654297</v>
+        <v>0.2480500936508179</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03964101523160934</v>
+        <v>0.1316239982843399</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1229805126786232</v>
+        <v>0.01315263286232948</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5056618452072144</v>
+        <v>1.276074886322021</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02611159905791283</v>
+        <v>0.003463611006736755</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2886894941329956</v>
+        <v>0.1631558984518051</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1205629259347916</v>
+        <v>0.1853587776422501</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3463774621486664</v>
+        <v>0.8113580942153931</v>
       </c>
       <c r="P3" t="n">
-        <v>0.09339256584644318</v>
+        <v>0.1151995584368706</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.02544900216162205</v>
+        <v>0.2090769708156586</v>
       </c>
       <c r="R3" t="n">
-        <v>0.07225716114044189</v>
+        <v>0.1002348586916924</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02628497779369354</v>
+        <v>0.1696416437625885</v>
       </c>
       <c r="T3" t="n">
-        <v>0.07854633778333664</v>
+        <v>0.1673875600099564</v>
       </c>
       <c r="U3" t="n">
-        <v>0.02792223542928696</v>
+        <v>0.3656960725784302</v>
       </c>
       <c r="V3" t="n">
-        <v>0.004213258158415556</v>
+        <v>0.1428800523281097</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01570075005292892</v>
+        <v>0.1094136759638786</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01966502331197262</v>
+        <v>0.1796992570161819</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.001875874120742083</v>
+        <v>0.4421098828315735</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.004182552918791771</v>
+        <v>0.1768743544816971</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02226461097598076</v>
+        <v>0.112411692738533</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0264466367661953</v>
+        <v>0.2589377760887146</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.1176215335726738</v>
+        <v>0.2316431701183319</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.003989293705672026</v>
+        <v>0.1485587656497955</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.01455951016396284</v>
+        <v>0.6663978695869446</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.06030353158712387</v>
+        <v>0.06327413022518158</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.02764599584043026</v>
+        <v>0.3422276377677917</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.0504441112279892</v>
+        <v>0.2380298376083374</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.002262827707454562</v>
+        <v>0.4407721161842346</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.00638172309845686</v>
+        <v>0.3444565534591675</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.01429380103945732</v>
+        <v>0.07714609056711197</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.05643200874328613</v>
+        <v>0.2075991928577423</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.01125840283930302</v>
+        <v>0.01517356932163239</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.01412498205900192</v>
+        <v>0.07396380603313446</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.01290510781109333</v>
+        <v>0.1174270510673523</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.08420258760452271</v>
+        <v>0.3055806756019592</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.007890191860496998</v>
+        <v>0.3016729950904846</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.001635495573282242</v>
+        <v>0.2211272865533829</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.03976228833198547</v>
+        <v>0.05395127460360527</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.07657036930322647</v>
+        <v>0.04719829559326172</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.4311286509037018</v>
+        <v>0.9425550103187561</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.03998864069581032</v>
+        <v>0.145393118262291</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.01046800147742033</v>
+        <v>0.07154087722301483</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.0657496303319931</v>
+        <v>0.4417769014835358</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.2879281044006348</v>
+        <v>0.7118001580238342</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.01357055455446243</v>
+        <v>0.2323101758956909</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.02599536068737507</v>
+        <v>0.007330066524446011</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.07798042148351669</v>
+        <v>0.1854455471038818</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.02390413917601109</v>
+        <v>0.1574301868677139</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.1081226468086243</v>
+        <v>0.3088541924953461</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.1138389185070992</v>
+        <v>0.1845966279506683</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.07379226386547089</v>
+        <v>0.4499125182628632</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.06770224869251251</v>
+        <v>0.2352383136749268</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.1286274641752243</v>
+        <v>0.343086838722229</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.07642257213592529</v>
+        <v>0.02800777554512024</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.01300476491451263</v>
+        <v>0.2379100918769836</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.01510922238230705</v>
+        <v>0.1036030203104019</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.03239190578460693</v>
+        <v>0.1590235531330109</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.02081646770238876</v>
+        <v>0.05899864435195923</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.007565166801214218</v>
+        <v>0.06741998344659805</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.08441774547100067</v>
+        <v>0.04704326391220093</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.04101346805691719</v>
+        <v>0.110123798251152</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.02550994604825974</v>
+        <v>0.2231818288564682</v>
       </c>
       <c r="BR3" t="n">
-        <v>5.791150033473969e-05</v>
+        <v>0.1403645277023315</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.06012497842311859</v>
+        <v>0.1082892268896103</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.007778366096317768</v>
+        <v>0.1253927499055862</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.04398077353835106</v>
+        <v>0.07153093069791794</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.196619987487793</v>
+        <v>0.4090105295181274</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.06191930919885635</v>
+        <v>0.295142650604248</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.008109506219625473</v>
+        <v>0.01368890888988972</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.10099808126688</v>
+        <v>0.1765688061714172</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.09673118591308594</v>
+        <v>0.5196309685707092</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.02326332591474056</v>
+        <v>0.5356415510177612</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.03233522921800613</v>
+        <v>0.06657189130783081</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.01277792174369097</v>
+        <v>0.005624428391456604</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.002670240122824907</v>
+        <v>0.0403960645198822</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.1253023147583008</v>
+        <v>0.3701566755771637</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.03104910627007484</v>
+        <v>0.02360459789633751</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.02689017727971077</v>
+        <v>0.06600256264209747</v>
       </c>
       <c r="CH3" t="n">
-        <v>2.810265868902206e-05</v>
+        <v>0.0925782173871994</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.05715669319033623</v>
+        <v>0.2132420688867569</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.003186680376529694</v>
+        <v>0.01812693849205971</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.005017696879804134</v>
+        <v>0.05987479537725449</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.002854349091649055</v>
+        <v>0.02395572140812874</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.09649299085140228</v>
+        <v>0.2867796421051025</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.01466972753405571</v>
+        <v>0.6027113199234009</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.005415226332843304</v>
+        <v>0.4572628140449524</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.002271723002195358</v>
+        <v>0.4465113282203674</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.02483458258211613</v>
+        <v>0.157371461391449</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.01591239124536514</v>
+        <v>0.3237948715686798</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.03272435814142227</v>
+        <v>0.0502043217420578</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.07201288640499115</v>
+        <v>0.2118390798568726</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.007346848957240582</v>
+        <v>0.2351443469524384</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.0115770036354661</v>
+        <v>0.003762143198400736</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.1006831675767899</v>
+        <v>0.3514615893363953</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.04273771494626999</v>
+        <v>0.03907782584428787</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.05548462644219398</v>
+        <v>0.02292921952903271</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.007084829267114401</v>
+        <v>0.0714055523276329</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.06445415318012238</v>
+        <v>0.1892741918563843</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.01437442190945148</v>
+        <v>0.01078421995043755</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.0001024845987558365</v>
+        <v>0.01094096805900335</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.004046544898301363</v>
+        <v>0.005031322129070759</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.005663606338202953</v>
+        <v>0.4810567498207092</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.04091238602995872</v>
+        <v>0.2046439796686172</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.05130827054381371</v>
+        <v>0.3090502619743347</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.02395967394113541</v>
+        <v>0.1692565232515335</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.04069669544696808</v>
+        <v>0.2159444093704224</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.08389828354120255</v>
+        <v>0.832897961139679</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.01848017796874046</v>
+        <v>0.2483397722244263</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.172842264175415</v>
+        <v>0.2591423988342285</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.04299326986074448</v>
+        <v>0.2794806957244873</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.001601564697921276</v>
+        <v>0.02651102095842361</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.01202974747866392</v>
+        <v>0.1603510677814484</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.06028931960463524</v>
+        <v>0.08160114288330078</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.01511712558567524</v>
+        <v>0.1323683708906174</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.01210556738078594</v>
+        <v>0.006073922850191593</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.04940371960401535</v>
+        <v>0.0230735931545496</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.0458470992743969</v>
+        <v>0.01457272097468376</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.005469087511301041</v>
+        <v>0.00816130917519331</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.0316169410943985</v>
+        <v>0.04492191970348358</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.01842004433274269</v>
+        <v>0.139460876584053</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.07701465487480164</v>
+        <v>0.2478250414133072</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.02666011638939381</v>
+        <v>0.01560449600219727</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.007987439632415771</v>
+        <v>0.06743448972702026</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.01699189469218254</v>
+        <v>0.1960544139146805</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.0221122894436121</v>
+        <v>0.3183236122131348</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.01068514958024025</v>
+        <v>0.02785218134522438</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.05653021484613419</v>
+        <v>0.4533464014530182</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.01103366632014513</v>
+        <v>0.3734368681907654</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.01480626128613949</v>
+        <v>0.110156886279583</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.1096723973751068</v>
+        <v>0.1432972550392151</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.0159771665930748</v>
+        <v>0.1334311962127686</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.006044846028089523</v>
+        <v>0.3491627275943756</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.02792192250490189</v>
+        <v>0.09599070250988007</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.08415272831916809</v>
+        <v>0.1972421556711197</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.02009064704179764</v>
+        <v>0.08948901295661926</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.06847623735666275</v>
+        <v>0.1108254343271255</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.02043194882571697</v>
+        <v>0.06536920368671417</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.03032615035772324</v>
+        <v>0.07095462083816528</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.09490372240543365</v>
+        <v>0.2649378776550293</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.04696576297283173</v>
+        <v>0.3174369037151337</v>
       </c>
       <c r="ER3" t="n">
-        <v>0.02450723201036453</v>
+        <v>0.252061665058136</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.04235163331031799</v>
+        <v>0.3823803663253784</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.09804776310920715</v>
+        <v>0.3007274866104126</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.04039384424686432</v>
+        <v>0.0664806067943573</v>
       </c>
       <c r="EV3" t="n">
-        <v>0.03838498145341873</v>
+        <v>0.1207218691706657</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.05438626557588577</v>
+        <v>0.09118091315031052</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.01748479716479778</v>
+        <v>0.02152322977781296</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.1116679832339287</v>
+        <v>0.3386621475219727</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.01433710940182209</v>
+        <v>0.04162424802780151</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.02693644911050797</v>
+        <v>0.02342466451227665</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.005028930492699146</v>
+        <v>0.1587405800819397</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.04690319299697876</v>
+        <v>0.2011210918426514</v>
       </c>
       <c r="FD3" t="n">
-        <v>0.00228935107588768</v>
+        <v>0.02640245854854584</v>
       </c>
       <c r="FE3" t="n">
-        <v>0.01569752767682076</v>
+        <v>0.03582512959837914</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.0007054479792714119</v>
+        <v>0.04804067686200142</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.03643407300114632</v>
+        <v>0.1962399780750275</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.01556164771318436</v>
+        <v>0.1160287111997604</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.03974631801247597</v>
+        <v>0.1406634896993637</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.06453872472047806</v>
+        <v>0.04025955498218536</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.02407311648130417</v>
+        <v>0.1436497271060944</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.04032783210277557</v>
+        <v>0.4489951729774475</v>
       </c>
       <c r="FM3" t="n">
-        <v>0.0317828431725502</v>
+        <v>0.1588335037231445</v>
       </c>
       <c r="FN3" t="n">
-        <v>0.03701101243495941</v>
+        <v>0.09701956808567047</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.06254315376281738</v>
+        <v>0.4695957899093628</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.03766734898090363</v>
+        <v>0.4174334406852722</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.2275557070970535</v>
+        <v>0.1153377443552017</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.0002883551642298698</v>
+        <v>0.007295906543731689</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.1092726588249207</v>
+        <v>0.09059447050094604</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.001757606863975525</v>
+        <v>0.1701826602220535</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.04307796433568001</v>
+        <v>0.07471169531345367</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.07104228436946869</v>
+        <v>0.3533775210380554</v>
       </c>
       <c r="FW3" t="n">
-        <v>0.0419757291674614</v>
+        <v>0.1915057003498077</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.001957220956683159</v>
+        <v>0.0971272736787796</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.08616475760936737</v>
+        <v>0.2929081618785858</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.05562904104590416</v>
+        <v>0.1439774930477142</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.01731475442647934</v>
+        <v>0.0789218470454216</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.01879521273076534</v>
+        <v>0.05010423809289932</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.2487002909183502</v>
+        <v>0.4892860054969788</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.1048422604799271</v>
+        <v>0.3195306658744812</v>
       </c>
       <c r="GE3" t="n">
-        <v>0.04712027311325073</v>
+        <v>0.1092019751667976</v>
       </c>
       <c r="GF3" t="n">
-        <v>0.002022663131356239</v>
+        <v>0.1062119081616402</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.0160147026181221</v>
+        <v>0.3585906326770782</v>
       </c>
     </row>
     <row r="4">
@@ -2706,1140 +2706,1140 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.001268246327526867</v>
+        <v>0.07953492552042007</v>
       </c>
       <c r="B5" t="n">
-        <v>0.01888186857104301</v>
+        <v>0.3114030659198761</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001294171437621117</v>
+        <v>0.1116523370146751</v>
       </c>
       <c r="D5" t="n">
-        <v>0.005742582492530346</v>
+        <v>0.000966288149356842</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006297532934695482</v>
+        <v>0.01779502630233765</v>
       </c>
       <c r="F5" t="n">
-        <v>0.009040824137628078</v>
+        <v>0.4199735224246979</v>
       </c>
       <c r="G5" t="n">
-        <v>0.000484441639855504</v>
+        <v>0.01411532238125801</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003715269034728408</v>
+        <v>0.07315020263195038</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0008802959928289056</v>
+        <v>0.05819005519151688</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001460740109905601</v>
+        <v>0.02749801799654961</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01896261982619762</v>
+        <v>0.3078994750976562</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00142154935747385</v>
+        <v>0.1569370329380035</v>
       </c>
       <c r="M5" t="n">
-        <v>0.009296822361648083</v>
+        <v>0.05095813423395157</v>
       </c>
       <c r="N5" t="n">
-        <v>0.008387723006308079</v>
+        <v>0.1308939754962921</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01129700057208538</v>
+        <v>0.461632639169693</v>
       </c>
       <c r="P5" t="n">
-        <v>0.004641844891011715</v>
+        <v>0.0176056232303381</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.003946087323129177</v>
+        <v>0.07943260669708252</v>
       </c>
       <c r="R5" t="n">
-        <v>0.001698749256320298</v>
+        <v>0.05913811177015305</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0008978834957815707</v>
+        <v>0.0147943077608943</v>
       </c>
       <c r="T5" t="n">
-        <v>0.003320991061627865</v>
+        <v>0.02494833804666996</v>
       </c>
       <c r="U5" t="n">
-        <v>0.000853630481287837</v>
+        <v>0.0708121657371521</v>
       </c>
       <c r="V5" t="n">
-        <v>0.001723183784633875</v>
+        <v>0.04927023127675056</v>
       </c>
       <c r="W5" t="n">
-        <v>0.001350324018858373</v>
+        <v>0.08852232247591019</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0001234881638083607</v>
+        <v>0.06834591180086136</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.001677765743806958</v>
+        <v>0.03362728655338287</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.001090013654902577</v>
+        <v>0.04627766087651253</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.001483457745052874</v>
+        <v>0.0365828275680542</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.002609720220789313</v>
+        <v>0.0531613864004612</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.002150921616703272</v>
+        <v>0.007333595305681229</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.00523555651307106</v>
+        <v>0.05058318376541138</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.003290369175374508</v>
+        <v>0.1568831205368042</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.00442283321171999</v>
+        <v>0.12355075776577</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.0005043677520006895</v>
+        <v>0.103143572807312</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.003593133296817541</v>
+        <v>0.008225107565522194</v>
       </c>
       <c r="AI5" t="n">
-        <v>6.888309144414961e-05</v>
+        <v>0.1559288203716278</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.002300871768966317</v>
+        <v>0.00804439652711153</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.0007483105873689055</v>
+        <v>0.009376060217618942</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.004981978330761194</v>
+        <v>0.09468373656272888</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.001764043932780623</v>
+        <v>0.05405637621879578</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.0009070888627320528</v>
+        <v>0.06515742093324661</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.004001082852482796</v>
+        <v>0.03876876831054688</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.001431471086107194</v>
+        <v>0.03809607774019241</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.0002683103375602514</v>
+        <v>0.01239776611328125</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.001251331064850092</v>
+        <v>0.005025401711463928</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.001269639935344458</v>
+        <v>0.07611306756734848</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.002781149465590715</v>
+        <v>0.003611873835325241</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.01238923333585262</v>
+        <v>0.1910610347986221</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.003074477892369032</v>
+        <v>0.1053460463881493</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.001560705248266459</v>
+        <v>0.003411716781556606</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.002708123065531254</v>
+        <v>0.2109427154064178</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.001243328093551099</v>
+        <v>0.2712141275405884</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.004344444256275892</v>
+        <v>0.03156697005033493</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.00227659847587347</v>
+        <v>0.003129167482256889</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.001493212766945362</v>
+        <v>0.03870343789458275</v>
       </c>
       <c r="BC5" t="n">
-        <v>9.393531217938289e-05</v>
+        <v>0.02411855012178421</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.005773032549768686</v>
+        <v>0.06322628259658813</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.001413637539371848</v>
+        <v>0.08519937098026276</v>
       </c>
       <c r="BF5" t="n">
-        <v>9.953722474165261e-05</v>
+        <v>0.0177274476736784</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.007530068978667259</v>
+        <v>0.07220864295959473</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.005063708405941725</v>
+        <v>0.005921763833612204</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.002661599544808269</v>
+        <v>0.01999184489250183</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.0005975111271254718</v>
+        <v>0.06955112516880035</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.0001013705623336136</v>
+        <v>0.01887398026883602</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.002148658270016313</v>
+        <v>0.01367880497127771</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.00318062724545598</v>
+        <v>0.006861433386802673</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.0001588681479915977</v>
+        <v>0.00575985899195075</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.001661246875301003</v>
+        <v>0.01906305551528931</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.00129793374799192</v>
+        <v>0.01340378634631634</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.0003033660177607089</v>
+        <v>0.06519835442304611</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.0008028930751606822</v>
+        <v>0.01002150774002075</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.0001504207029938698</v>
+        <v>0.00721361069008708</v>
       </c>
       <c r="BT5" t="n">
-        <v>3.93001246266067e-05</v>
+        <v>0.07510572671890259</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.001838542870245874</v>
+        <v>0.03364835307002068</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.007122078910470009</v>
+        <v>0.1522538661956787</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.0001539456425234675</v>
+        <v>0.05906825512647629</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.001508822897449136</v>
+        <v>0.06359561532735825</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.0001486582186771557</v>
+        <v>0.0628838911652565</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.0003539498138707131</v>
+        <v>0.1763091534376144</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.002883152570575476</v>
+        <v>0.03118185326457024</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.000366221385775134</v>
+        <v>0.01367765478789806</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.0009622338693588972</v>
+        <v>0.0459141694009304</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.0007116955821402371</v>
+        <v>0.02218850702047348</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.003269551321864128</v>
+        <v>0.0992371141910553</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.0003650671860668808</v>
+        <v>0.01436335407197475</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.00139799783937633</v>
+        <v>0.01925486139953136</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.0002215966815128922</v>
+        <v>0.004091372713446617</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.001235729781910777</v>
+        <v>0.09744811803102493</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.002190554514527321</v>
+        <v>0.005575483664870262</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.0002748366969171911</v>
+        <v>0.01668896898627281</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.0001906361867440864</v>
+        <v>0.03095629066228867</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.002266434021294117</v>
+        <v>0.04527273029088974</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.004178272094577551</v>
+        <v>0.06739379465579987</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.001286178943701088</v>
+        <v>0.1220991685986519</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.0006786415469832718</v>
+        <v>0.07615089416503906</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.000792738632299006</v>
+        <v>0.09761928766965866</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.002026413567364216</v>
+        <v>0.003938426729291677</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.004959345329552889</v>
+        <v>0.0483095571398735</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.008668928407132626</v>
+        <v>0.02158406749367714</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.002668386325240135</v>
+        <v>0.0004628589376807213</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.0007149730226956308</v>
+        <v>0.01398975495249033</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.002937151584774256</v>
+        <v>0.08344712108373642</v>
       </c>
       <c r="CX5" t="n">
-        <v>4.076052573509514e-05</v>
+        <v>0.02543360739946365</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.001529383240267634</v>
+        <v>0.01889887079596519</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.0001190749535453506</v>
+        <v>0.02565940655767918</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.001879656570963562</v>
+        <v>0.1069546043872833</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.001351061044260859</v>
+        <v>0.005780147388577461</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.0002010755124501884</v>
+        <v>0.0163377933204174</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.0004575683269649744</v>
+        <v>0.02508974820375443</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.000651999784167856</v>
+        <v>0.04765629768371582</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.002228662837296724</v>
+        <v>0.07945755124092102</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.004555230028927326</v>
+        <v>0.06706421822309494</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.0009377287933602929</v>
+        <v>0.01437811180949211</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.0001356785651296377</v>
+        <v>0.04304967075586319</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.004842487163841724</v>
+        <v>0.1164844930171967</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.003044816665351391</v>
+        <v>0.02456997893750668</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.0002590932999737561</v>
+        <v>0.07073057442903519</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.00105348089709878</v>
+        <v>0.02621075883507729</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.0001032728468999267</v>
+        <v>0.01930675655603409</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.002091178437694907</v>
+        <v>0.0632781907916069</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.001283441437408328</v>
+        <v>0.01031284779310226</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.00427046325057745</v>
+        <v>0.05379668995738029</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.000485668278997764</v>
+        <v>0.04811715707182884</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.003663095412775874</v>
+        <v>0.01815914735198021</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.002093020593747497</v>
+        <v>0.03218360990285873</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.002072741510346532</v>
+        <v>0.01784282177686691</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.0001607023586984724</v>
+        <v>0.0449720174074173</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.001700909808278084</v>
+        <v>0.01876662485301495</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.0002907766902353615</v>
+        <v>0.00423058494925499</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.0001063748204614967</v>
+        <v>0.08366298675537109</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.004406750667840242</v>
+        <v>0.0301432590931654</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.001216992968693376</v>
+        <v>0.01282426528632641</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.002768763341009617</v>
+        <v>0.08642353862524033</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.002032531192526221</v>
+        <v>0.01982294395565987</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.005140286404639482</v>
+        <v>0.03033006936311722</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.0006920677260495722</v>
+        <v>0.09762435406446457</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.0004869693657383323</v>
+        <v>0.001415142323821783</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.003043929813429713</v>
+        <v>0.0283061545342207</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.0002540204441174865</v>
+        <v>0.0330517590045929</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.0007356035057455301</v>
+        <v>0.09216143190860748</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.00043052903492935</v>
+        <v>0.02630310691893101</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.001081076799891889</v>
+        <v>0.0606066919863224</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.002662718528881669</v>
+        <v>0.01919279433786869</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.001059448230080307</v>
+        <v>0.009388882666826248</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.0002120754797942936</v>
+        <v>0.02414934150874615</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.000662099220789969</v>
+        <v>0.03080063685774803</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.002204646356403828</v>
+        <v>0.08042095601558685</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.001415311358869076</v>
+        <v>0.03716924786567688</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.001141939079388976</v>
+        <v>0.03196419775485992</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.003898124676197767</v>
+        <v>0.04994221031665802</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.00303954747505486</v>
+        <v>0.03293963521718979</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.0003616318281274289</v>
+        <v>0.02730801701545715</v>
       </c>
       <c r="EV5" t="n">
-        <v>5.241049439064227e-05</v>
+        <v>0.02097669802606106</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.001520808436907828</v>
+        <v>0.01010743249207735</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.0005296372692100704</v>
+        <v>0.02710103243589401</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.003091763006523252</v>
+        <v>0.09175635129213333</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.0002434823836665601</v>
+        <v>0.0181596577167511</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.001099154236726463</v>
+        <v>0.02087337151169777</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.0001554804766783491</v>
+        <v>0.003579623997211456</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.001516819698736072</v>
+        <v>0.09765323996543884</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.001573552377521992</v>
+        <v>0.01501591131091118</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.0009592347778379917</v>
+        <v>0.01213883981108665</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.0006572615238837898</v>
+        <v>0.0018279361538589</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.0004260482382960618</v>
+        <v>0.007973998785018921</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.001531140529550612</v>
+        <v>0.05473026260733604</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.0006108380039222538</v>
+        <v>0.06797561049461365</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.005385290831327438</v>
+        <v>0.01258575730025768</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.002835908439010382</v>
+        <v>0.004237664863467216</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.002018705708906054</v>
+        <v>0.1327415108680725</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.002423823811113834</v>
+        <v>0.04593368247151375</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.003488102229312062</v>
+        <v>0.07064525038003922</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.001657220302149653</v>
+        <v>0.1343434005975723</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.0006646309047937393</v>
+        <v>0.04513384774327278</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.008206634782254696</v>
+        <v>0.07480791211128235</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.0008929843315854669</v>
+        <v>0.08890719711780548</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.003764783265069127</v>
+        <v>0.02806620858609676</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.003796037286520004</v>
+        <v>0.134893000125885</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.00151974312029779</v>
+        <v>0.1012023389339447</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.003261900972574949</v>
+        <v>0.03787077590823174</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.002000676468014717</v>
+        <v>0.1578388959169388</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.001333662308752537</v>
+        <v>0.06158467009663582</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.001759701641276479</v>
+        <v>0.06725132465362549</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.002349411137402058</v>
+        <v>0.02294042520225048</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.004034532699733973</v>
+        <v>0.09150511026382446</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.000431941996794194</v>
+        <v>0.01059366669505835</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.001249405322596431</v>
+        <v>0.1323399841785431</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.0002874922065529972</v>
+        <v>0.1200401335954666</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.0006094096461310983</v>
+        <v>0.02546489052474499</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.002108735032379627</v>
+        <v>0.04384547099471092</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.0005444562993943691</v>
+        <v>0.05200424417853355</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.004932221490889788</v>
+        <v>0.8636349439620972</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1898225396871567</v>
+        <v>1.120060324668884</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01449986826628447</v>
+        <v>0.1161979883909225</v>
       </c>
       <c r="D6" t="n">
-        <v>0.07716482877731323</v>
+        <v>0.1171437650918961</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01066528726369143</v>
+        <v>0.01839859038591385</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1650325357913971</v>
+        <v>0.8664892315864563</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01371394842863083</v>
+        <v>0.2296464890241623</v>
       </c>
       <c r="H6" t="n">
-        <v>0.08047300577163696</v>
+        <v>0.3691596984863281</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01407560892403126</v>
+        <v>0.3577456176280975</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02220493927598</v>
+        <v>0.8364109396934509</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1832575500011444</v>
+        <v>1.393591284751892</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003145907539874315</v>
+        <v>0.156099408864975</v>
       </c>
       <c r="M6" t="n">
-        <v>0.09305348992347717</v>
+        <v>0.1092745363712311</v>
       </c>
       <c r="N6" t="n">
-        <v>0.007104950957000256</v>
+        <v>0.3967927098274231</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1623567640781403</v>
+        <v>0.801516056060791</v>
       </c>
       <c r="P6" t="n">
-        <v>0.02702409215271473</v>
+        <v>0.2553668916225433</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01718476787209511</v>
+        <v>0.01941695436835289</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0005736001767218113</v>
+        <v>0.6244621872901917</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01443895511329174</v>
+        <v>0.03531496226787567</v>
       </c>
       <c r="T6" t="n">
-        <v>0.02026915922760963</v>
+        <v>0.1620399653911591</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0005400963127613068</v>
+        <v>0.2136347144842148</v>
       </c>
       <c r="V6" t="n">
-        <v>0.00389213371090591</v>
+        <v>0.3472588062286377</v>
       </c>
       <c r="W6" t="n">
-        <v>0.008972059935331345</v>
+        <v>0.2215798497200012</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01602454856038094</v>
+        <v>0.180453360080719</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01321648433804512</v>
+        <v>0.03864733129739761</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0016173105686903</v>
+        <v>0.398836225271225</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.02468407154083252</v>
+        <v>0.2116890996694565</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.008612962439656258</v>
+        <v>0.2750498652458191</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.02078202925622463</v>
+        <v>0.2504262924194336</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.02359092049300671</v>
+        <v>0.1378013789653778</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.01433536875993013</v>
+        <v>0.4012756049633026</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.008822694420814514</v>
+        <v>0.6396960020065308</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.005113531835377216</v>
+        <v>0.2194878160953522</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.02235891111195087</v>
+        <v>0.04852322489023209</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.01412278134375811</v>
+        <v>0.3550346493721008</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.002686973894014955</v>
+        <v>0.1469587087631226</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.005677321925759315</v>
+        <v>0.2805664241313934</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.04647911712527275</v>
+        <v>0.3411125242710114</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.007724990136921406</v>
+        <v>0.2456629872322083</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.000840943306684494</v>
+        <v>0.2970022559165955</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.02896258607506752</v>
+        <v>0.2324348539113998</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.02558047324419022</v>
+        <v>0.04510968178510666</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.00688134552910924</v>
+        <v>0.1916458606719971</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.01913195848464966</v>
+        <v>0.30733722448349</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.003082676092162728</v>
+        <v>0.2979454100131989</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.03115141950547695</v>
+        <v>0.5968342423439026</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.1228957697749138</v>
+        <v>0.9323662519454956</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.01624429039657116</v>
+        <v>0.1605885773897171</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.01750245131552219</v>
+        <v>0.07523828744888306</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.03112085163593292</v>
+        <v>0.3253380060195923</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.06633980572223663</v>
+        <v>0.2668015658855438</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.025214908644557</v>
+        <v>0.04609113559126854</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.01098111923784018</v>
+        <v>0.00113532249815762</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.005828133318573236</v>
+        <v>0.2472265511751175</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.01415569987148046</v>
+        <v>0.1029897481203079</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.04559669271111488</v>
+        <v>0.1482351273298264</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.03116260655224323</v>
+        <v>0.1636449098587036</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.005055993795394897</v>
+        <v>0.1446899175643921</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.04484116286039352</v>
+        <v>0.03271010518074036</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.05225097015500069</v>
+        <v>0.3805407583713531</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.03446203097701073</v>
+        <v>0.007698997855186462</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.00206539174541831</v>
+        <v>0.102680116891861</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.002427323255687952</v>
+        <v>0.2271106988191605</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.007142340764403343</v>
+        <v>0.04638613760471344</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.006949727423489094</v>
+        <v>0.04135482013225555</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.002231921069324017</v>
+        <v>0.008026203140616417</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.01709442958235741</v>
+        <v>0.1830549240112305</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.02369935996830463</v>
+        <v>0.002031188458204269</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.00102859316393733</v>
+        <v>0.0999315157532692</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.005232838913798332</v>
+        <v>0.5804556012153625</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.003805397544056177</v>
+        <v>0.1532718390226364</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.001796131022274494</v>
+        <v>0.1718482673168182</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.0227385014295578</v>
+        <v>0.2068303525447845</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.06776896864175797</v>
+        <v>0.6452856659889221</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.00419175997376442</v>
+        <v>0.165077269077301</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.01765240542590618</v>
+        <v>0.296957403421402</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.001646894495934248</v>
+        <v>0.08041824400424957</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.03729819133877754</v>
+        <v>0.3831470608711243</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.01237975247204304</v>
+        <v>0.0001514293253421783</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.01569378934800625</v>
+        <v>0.09612081944942474</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.01948502659797668</v>
+        <v>0.2314204126596451</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.008752092719078064</v>
+        <v>0.1356184929609299</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.02973860688507557</v>
+        <v>0.3767073154449463</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.006785744801163673</v>
+        <v>0.04655149206519127</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.01874200999736786</v>
+        <v>0.05784978345036507</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.003696825820952654</v>
+        <v>0.08604705333709717</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.02938856743276119</v>
+        <v>0.2576822638511658</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.01076326239854097</v>
+        <v>0.2155863344669342</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.007550512440502644</v>
+        <v>0.1069915294647217</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.009911173954606056</v>
+        <v>0.0757746696472168</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.01289779972285032</v>
+        <v>0.0288250744342804</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.0117204524576664</v>
+        <v>0.5777968168258667</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.002620693063363433</v>
+        <v>0.09880159050226212</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.01754024811089039</v>
+        <v>0.4275470376014709</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.001761631923727691</v>
+        <v>0.1126582399010658</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.007606321480125189</v>
+        <v>0.2896370589733124</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.03329448774456978</v>
+        <v>0.1048361361026764</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.05011508241295815</v>
+        <v>0.0120843481272459</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.02519439905881882</v>
+        <v>0.003120830282568932</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.005506737623363733</v>
+        <v>0.09781467169523239</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.02598310820758343</v>
+        <v>0.3427249193191528</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.006660924758762121</v>
+        <v>0.06849977374076843</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.02293020486831665</v>
+        <v>0.04339851066470146</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.000665037427097559</v>
+        <v>0.05908817052841187</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.03212658315896988</v>
+        <v>0.250690221786499</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.005310836248099804</v>
+        <v>0.1572985053062439</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.01222139410674572</v>
+        <v>0.1616602689027786</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.004663512110710144</v>
+        <v>0.09117321670055389</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.003479412291198969</v>
+        <v>0.1063231006264687</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.0314556211233139</v>
+        <v>0.09134832769632339</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.02811651490628719</v>
+        <v>0.1798714995384216</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.02948220074176788</v>
+        <v>0.08091716468334198</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.01745802350342274</v>
+        <v>0.72095787525177</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.04047401621937752</v>
+        <v>0.1981964856386185</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.03619904816150665</v>
+        <v>0.04338791966438293</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.02560694143176079</v>
+        <v>0.09781252592802048</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.01714598946273327</v>
+        <v>0.320030152797699</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.003848948981612921</v>
+        <v>0.07727591693401337</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.01185567118227482</v>
+        <v>0.2364700436592102</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.01338452007621527</v>
+        <v>0.1453083604574203</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.03327208012342453</v>
+        <v>0.008970558643341064</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.01100332196801901</v>
+        <v>0.08292604237794876</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.02794468402862549</v>
+        <v>0.4514788389205933</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.01267415937036276</v>
+        <v>0.1330846101045609</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.0009427815675735474</v>
+        <v>0.4289538562297821</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.009908542037010193</v>
+        <v>0.1037719249725342</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.01458247378468513</v>
+        <v>0.1929540634155273</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.001216817181557417</v>
+        <v>0.06515904515981674</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.01117919012904167</v>
+        <v>0.06481257081031799</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.02940637245774269</v>
+        <v>0.2693314254283905</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.01304240059107542</v>
+        <v>0.4889097213745117</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.01073440536856651</v>
+        <v>0.4682700932025909</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.01158780232071877</v>
+        <v>0.0845508798956871</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.01657870598137379</v>
+        <v>0.04253055155277252</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.01393055450171232</v>
+        <v>0.2015915066003799</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.01005784329026937</v>
+        <v>0.1586092412471771</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.02665960788726807</v>
+        <v>0.02229458466172218</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.008283111266791821</v>
+        <v>0.1928273439407349</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.01336620654910803</v>
+        <v>0.4075630307197571</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.00684764888137579</v>
+        <v>0.08841921389102936</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.02303477935492992</v>
+        <v>0.1328861117362976</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.01427608076483011</v>
+        <v>0.1304731518030167</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.003580819815397263</v>
+        <v>0.08293493837118149</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.003910223487764597</v>
+        <v>0.09996037185192108</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.007427304051816463</v>
+        <v>0.08759180456399918</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.01638954132795334</v>
+        <v>0.1185992211103439</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.00901314802467823</v>
+        <v>0.07258940488100052</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.02340961247682571</v>
+        <v>0.09457920491695404</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.009231012314558029</v>
+        <v>0.08431277424097061</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.03447864577174187</v>
+        <v>0.280241996049881</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.0009439600398764014</v>
+        <v>0.05028608441352844</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.02665995433926582</v>
+        <v>0.1062066704034805</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.002098522614687681</v>
+        <v>0.3349700272083282</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.005194978788495064</v>
+        <v>0.1357068568468094</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.02557485178112984</v>
+        <v>0.4187749326229095</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.002391077112406492</v>
+        <v>0.02991458214819431</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.01829194091260433</v>
+        <v>0.03595252707600594</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.004556941799819469</v>
+        <v>0.110306516289711</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.02545879781246185</v>
+        <v>0.2328041642904282</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.01437165774405003</v>
+        <v>0.191430389881134</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.004609732888638973</v>
+        <v>0.1737831234931946</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.00692880479618907</v>
+        <v>0.02426589839160442</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.002191271865740418</v>
+        <v>0.0146636925637722</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.02023151703178883</v>
+        <v>0.5111634135246277</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.003231680020689964</v>
+        <v>0.1996127665042877</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.02624651789665222</v>
+        <v>0.0413845106959343</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.002686031861230731</v>
+        <v>0.1543094366788864</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.001159018371254206</v>
+        <v>0.3750777542591095</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.01605894416570663</v>
+        <v>0.1679702401161194</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.01777923107147217</v>
+        <v>0.6480826139450073</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.004461050964891911</v>
+        <v>0.001674830913543701</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.007723974995315075</v>
+        <v>0.326799213886261</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.07278414070606232</v>
+        <v>0.3608547747135162</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.003897509071975946</v>
+        <v>0.6935431957244873</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.03566141426563263</v>
+        <v>0.5318142175674438</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.02268661744892597</v>
+        <v>0.1626697182655334</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.01974439062178135</v>
+        <v>0.3507183790206909</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.03734816983342171</v>
+        <v>0.2523939907550812</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.01480162516236305</v>
+        <v>0.04944276064634323</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.002250397112220526</v>
+        <v>0.1426520049571991</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.006912993267178535</v>
+        <v>0.1821093559265137</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.01764107309281826</v>
+        <v>0.1709763556718826</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.01959363557398319</v>
+        <v>0.121822826564312</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.002422645222395658</v>
+        <v>0.2067722529172897</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.05367186293005943</v>
+        <v>0.3413516581058502</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.01839788630604744</v>
+        <v>0.1851273477077484</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.04627528414130211</v>
+        <v>0.04264245927333832</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.01780795678496361</v>
+        <v>0.304711788892746</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.007702364586293697</v>
+        <v>0.4337702989578247</v>
       </c>
     </row>
     <row r="7">
@@ -4413,571 +4413,571 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.006337128579616547</v>
+        <v>0.002793760737404227</v>
       </c>
       <c r="B8" t="n">
-        <v>0.2254987955093384</v>
+        <v>0.004564096219837666</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009193019941449165</v>
+        <v>0.0002890952455345541</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03352408483624458</v>
+        <v>9.059111471287906e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01962108910083771</v>
+        <v>0.000308002985548228</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1867953240871429</v>
+        <v>0.001103020971640944</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03120177611708641</v>
+        <v>0.000536727427970618</v>
       </c>
       <c r="H8" t="n">
-        <v>0.07849646359682083</v>
+        <v>9.554979624226689e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05664204061031342</v>
+        <v>0.0006526765646412969</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01588759571313858</v>
+        <v>0.002221315167844296</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2068288028240204</v>
+        <v>0.004739168100059032</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001409073360264301</v>
+        <v>0.0001964940747711807</v>
       </c>
       <c r="M8" t="n">
-        <v>0.053302101790905</v>
+        <v>0.0006503326585516334</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01607435941696167</v>
+        <v>0.001419986365363002</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1847093254327774</v>
+        <v>0.00150603661313653</v>
       </c>
       <c r="P8" t="n">
-        <v>0.02962636016309261</v>
+        <v>8.658327715238556e-06</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.02320015802979469</v>
+        <v>0.0005219585727900267</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03362365812063217</v>
+        <v>0.001682489295490086</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01826328411698341</v>
+        <v>0.0003764087741728872</v>
       </c>
       <c r="T8" t="n">
-        <v>0.000622984953224659</v>
+        <v>0.0001585973368491977</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0411359928548336</v>
+        <v>0.0007091936422511935</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001159008592367172</v>
+        <v>0.0005717964377254248</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01536037307232618</v>
+        <v>0.0009886082261800766</v>
       </c>
       <c r="X8" t="n">
-        <v>0.03183647617697716</v>
+        <v>0.0004160521784797311</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0124373733997345</v>
+        <v>0.0005464937421493232</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01068171020597219</v>
+        <v>0.0008995830430649221</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01394857279956341</v>
+        <v>0.0003413242811802775</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.02105667628347874</v>
+        <v>0.0002812989696394652</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.02981680072844028</v>
+        <v>0.0004794065607711673</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.02669145911931992</v>
+        <v>0.0001278504205401987</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.008495443500578403</v>
+        <v>0.001669254968874156</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.02539194002747536</v>
+        <v>0.001574432477355003</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.01702799648046494</v>
+        <v>1.271796645596623e-05</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.00434259744361043</v>
+        <v>0.0005651944666169584</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.005457638762891293</v>
+        <v>0.0007998355431482196</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.006828974466770887</v>
+        <v>0.0004940155195072293</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.01838987693190575</v>
+        <v>0.0009976299479603767</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.0144340768456459</v>
+        <v>0.0005447391304187477</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.04749506339430809</v>
+        <v>0.0005757728940807283</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.002310731448233128</v>
+        <v>0.001278810668736696</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.0257717277854681</v>
+        <v>8.738425094634295e-05</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.02245712280273438</v>
+        <v>0.000403140380512923</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.02098400704562664</v>
+        <v>0.000600631523411721</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.01671953126788139</v>
+        <v>0.0001715867256280035</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.01340599916875362</v>
+        <v>0.0003131895209662616</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.02026968076825142</v>
+        <v>0.001657508546486497</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.1769330352544785</v>
+        <v>0.002686477266252041</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.06777129322290421</v>
+        <v>0.0001346675271634012</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.01691693067550659</v>
+        <v>0.000353407405782491</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.06824196875095367</v>
+        <v>0.001226591528393328</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.01834611035883427</v>
+        <v>0.0004493595915846527</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.0356488935649395</v>
+        <v>0.00021023114095442</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.0226062498986721</v>
+        <v>0.0007244934677146375</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.0262183453887701</v>
+        <v>0.0006048576324246824</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.01821441762149334</v>
+        <v>0.0008363929227925837</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.07222583889961243</v>
+        <v>0.001405902672559023</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.04024336114525795</v>
+        <v>0.0008401881204918027</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.01077222637832165</v>
+        <v>0.0001639671972952783</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.01660175621509552</v>
+        <v>0.0007088452111929655</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.1281514018774033</v>
+        <v>0.001297649694606662</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.01179775595664978</v>
+        <v>0.0006679773214273155</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.01138666365295649</v>
+        <v>0.000330671900883317</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.02578276209533215</v>
+        <v>0.000374165247194469</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.02819574996829033</v>
+        <v>0.0003805329906754196</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.007405277341604233</v>
+        <v>7.021735655143857e-06</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.01272223703563213</v>
+        <v>0.0001518024946562946</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.01843443140387535</v>
+        <v>9.621614299248904e-05</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.01800062507390976</v>
+        <v>0.0006170472479425371</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.01502933539450169</v>
+        <v>1.563895057188347e-05</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.02527914196252823</v>
+        <v>0.0008039084495976567</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.01050795987248421</v>
+        <v>0.0003165004309266806</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.006882955320179462</v>
+        <v>0.0007058389601297677</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.006257204804569483</v>
+        <v>0.001789703266695142</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.07905381172895432</v>
+        <v>0.001686448231339455</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.05140092223882675</v>
+        <v>0.0002968672779388726</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.01550669316202402</v>
+        <v>0.000460973649751395</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.03606528788805008</v>
+        <v>9.561442857375368e-05</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.01271382812410593</v>
+        <v>0.001037841895595193</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.002099876990541816</v>
+        <v>0.0005672911647707224</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.00547025864943862</v>
+        <v>5.419482477009296e-06</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.009033834561705589</v>
+        <v>0.0004255240201018751</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.004371790681034327</v>
+        <v>0.0009189356351271272</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.03079241141676903</v>
+        <v>0.001315702684223652</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.007346308790147305</v>
+        <v>0.0003100704052485526</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.0004112794995307922</v>
+        <v>0.0002540891291573644</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.006892998702824116</v>
+        <v>0.0001217699318658561</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.03955304995179176</v>
+        <v>0.0004431548295542598</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.009766392409801483</v>
+        <v>0.0003063723561353981</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.009433463215827942</v>
+        <v>5.538540426641703e-05</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.0005277765449136496</v>
+        <v>0.00016155002231244</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.002097209915518761</v>
+        <v>0.0001203625579364598</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.0422283411026001</v>
+        <v>0.001623836578801274</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.0009661060757935047</v>
+        <v>0.0006571247358806431</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.02990847453474998</v>
+        <v>0.000752865569666028</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.01854408532381058</v>
+        <v>0.0009392218198627234</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.001685178256593645</v>
+        <v>0.001643707742914557</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.02139819040894508</v>
+        <v>0.0002263393544126302</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.06120843067765236</v>
+        <v>3.873909008689225e-06</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.03041131980717182</v>
+        <v>0.0001338869333267212</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.0008503708522766829</v>
+        <v>0.00079346913844347</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.02746818214654922</v>
+        <v>0.001247880863957107</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.01196713373064995</v>
+        <v>0.0003607941616792232</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.006669678259640932</v>
+        <v>0.0001488218258600682</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.0008493888890370727</v>
+        <v>9.54875722527504e-05</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.04332128539681435</v>
+        <v>0.0004536155902314931</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.004196921829134226</v>
+        <v>9.226093243341893e-05</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.007144023664295673</v>
+        <v>0.0003667263954412192</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.008369290269911289</v>
+        <v>0.0001014611552818678</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.0294332280755043</v>
+        <v>0.0001544817932881415</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.02797146700322628</v>
+        <v>0.0007373298867605627</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.0008516790112480521</v>
+        <v>0.0001671395148150623</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.07179829478263855</v>
+        <v>0.0005837520584464073</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.03898718953132629</v>
+        <v>0.002240159315988421</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.04915980249643326</v>
+        <v>5.327313556335866e-05</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.01099661365151405</v>
+        <v>0.0003963969938922673</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.03705263882875443</v>
+        <v>0.0004113010363653302</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.04561534151434898</v>
+        <v>0.0006752414628863335</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.02728332579135895</v>
+        <v>0.0001479745405958965</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.01646589487791061</v>
+        <v>0.00094076112145558</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.002617180580273271</v>
+        <v>0.000495751912239939</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.01179766841232777</v>
+        <v>0.0002056500088656321</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.01793369278311729</v>
+        <v>0.0005128709017299116</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.02808619849383831</v>
+        <v>0.001129318377934396</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.01096764858812094</v>
+        <v>1.43067836688715e-05</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.0006651575677096844</v>
+        <v>0.001019933610223234</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.01022319961339235</v>
+        <v>0.0005495699006132782</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.01527922227978706</v>
+        <v>0.0005276813171803951</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.01894515193998814</v>
+        <v>0.0004253237566445023</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.003412352874875069</v>
+        <v>2.935584052465856e-05</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.008498013019561768</v>
+        <v>0.0007670184131711721</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.008117343299090862</v>
+        <v>0.0003367153403814882</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.004465238191187382</v>
+        <v>0.0004364040796644986</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.01008559670299292</v>
+        <v>0.0002899424580391496</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.03763343766331673</v>
+        <v>0.001055984757840633</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.03974058479070663</v>
+        <v>0.0004381639882922173</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.002716139424592257</v>
+        <v>0.0008205726044252515</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.04307126626372337</v>
+        <v>0.0001515398325864226</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.02970799058675766</v>
+        <v>0.0005557918921113014</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.01639493927359581</v>
+        <v>9.137696906691417e-05</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.01502093859016895</v>
+        <v>7.666094461455941e-05</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.01574276015162468</v>
+        <v>0.000224051414988935</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.006429391447454691</v>
+        <v>2.36811647482682e-05</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.002870905678719282</v>
+        <v>8.887869626050815e-05</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.001762071740813553</v>
+        <v>0.0001869551342679188</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.01953715085983276</v>
+        <v>0.001065429765731096</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.02057600952684879</v>
+        <v>0.0004189733299426734</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.03717704117298126</v>
+        <v>0.0006306847208179533</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.01076085679233074</v>
+        <v>0.0003026677004527301</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.03111697733402252</v>
+        <v>0.0009653017041273415</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.02979939430952072</v>
+        <v>0.00103825272526592</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.03318275511264801</v>
+        <v>0.0002554914972279221</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.03001009859144688</v>
+        <v>7.545626431237906e-05</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.0236916970461607</v>
+        <v>0.0008564364979974926</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.003600636031478643</v>
+        <v>0.0009923537727445364</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.02302149496972561</v>
+        <v>0.001384869334287941</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.0155611913651228</v>
+        <v>0.0001936801127158105</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.00718779768794775</v>
+        <v>0.0001786556967999786</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.01320209540426731</v>
+        <v>0.0003464906185399741</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.03791967406868935</v>
+        <v>0.0003345288569107652</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.004149205982685089</v>
+        <v>0.000330365845002234</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.001462555024772882</v>
+        <v>0.0001965806732187048</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.008435643278062344</v>
+        <v>4.911233554594219e-05</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.003581511089578271</v>
+        <v>0.0001943908573593944</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.008022638037800789</v>
+        <v>0.001215905882418156</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.04107564687728882</v>
+        <v>0.0004631021292880177</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.006455433554947376</v>
+        <v>0.00042571677477099</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.001655264990404248</v>
+        <v>7.438144530169666e-05</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.02253260090947151</v>
+        <v>0.001088239601813257</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.01649437844753265</v>
+        <v>0.0002820602676365525</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.01552555710077286</v>
+        <v>0.0004940066137351096</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.006691554095596075</v>
+        <v>0.0003828892949968576</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.01940113864839077</v>
+        <v>0.001169057562947273</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.03730789944529533</v>
+        <v>0.001676000305451453</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.05847295001149178</v>
+        <v>0.0005782998632639647</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.05493466556072235</v>
+        <v>0.001159814652055502</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.003595026675611734</v>
+        <v>0.0003734462952706963</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.008629857562482357</v>
+        <v>0.000953791372012347</v>
       </c>
       <c r="FV8" t="n">
-        <v>0.001056245295330882</v>
+        <v>0.000756732770241797</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.03043125197291374</v>
+        <v>0.001314176712185144</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.01018489710986614</v>
+        <v>0.0005817479686811566</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.02536481246352196</v>
+        <v>0.001027692575007677</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.03382181748747826</v>
+        <v>7.67125966376625e-05</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.02103947475552559</v>
+        <v>0.0004494836321100593</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.0370052307844162</v>
+        <v>0.0004061834188178182</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.04313221201300621</v>
+        <v>9.800304542295635e-05</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.01859639957547188</v>
+        <v>0.0006592107238247991</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.02941064722836018</v>
+        <v>0.0005938740214332938</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.01275361236184835</v>
+        <v>0.0001359490270260721</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.02252228558063507</v>
+        <v>0.001248595654033124</v>
       </c>
     </row>
     <row r="9">
@@ -5551,3984 +5551,2846 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.135311633348465</v>
+        <v>0.001045734737999737</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1653430908918381</v>
+        <v>0.01091835834085941</v>
       </c>
       <c r="C10" t="n">
-        <v>0.006502175703644753</v>
+        <v>0.004865937866270542</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2344082593917847</v>
+        <v>0.0005097526591271162</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3852380514144897</v>
+        <v>0.001649743877351284</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2809660732746124</v>
+        <v>0.009020796045660973</v>
       </c>
       <c r="G10" t="n">
-        <v>0.100064180791378</v>
+        <v>0.002545307856053114</v>
       </c>
       <c r="H10" t="n">
-        <v>0.06730915606021881</v>
+        <v>0.009127142839133739</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1554788500070572</v>
+        <v>0.001645143725909293</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1350819319486618</v>
+        <v>0.0002872382756322622</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1612603813409805</v>
+        <v>0.009877542033791542</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03342124447226524</v>
+        <v>0.0005691769765689969</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1291160881519318</v>
+        <v>0.002646136563271284</v>
       </c>
       <c r="N10" t="n">
-        <v>0.09268695861101151</v>
+        <v>0.005531379487365484</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1744633466005325</v>
+        <v>0.007124464027583599</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1130634695291519</v>
+        <v>0.0006074244156479836</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1826255917549133</v>
+        <v>0.007848684675991535</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1225968599319458</v>
+        <v>0.002788319485262036</v>
       </c>
       <c r="S10" t="n">
-        <v>0.03870095312595367</v>
+        <v>0.0003783231659326702</v>
       </c>
       <c r="T10" t="n">
-        <v>0.04019620642066002</v>
+        <v>0.00515070091933012</v>
       </c>
       <c r="U10" t="n">
-        <v>0.08046405762434006</v>
+        <v>0.001420666230842471</v>
       </c>
       <c r="V10" t="n">
-        <v>0.236250713467598</v>
+        <v>0.002262740395963192</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1719375401735306</v>
+        <v>0.003347669960930943</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1072051748633385</v>
+        <v>0.001572323148138821</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.1276056170463562</v>
+        <v>0.000258536369074136</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.01452457625418901</v>
+        <v>0.002010673051699996</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.04016236960887909</v>
+        <v>0.0003067405486945063</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.12892746925354</v>
+        <v>0.00110895955003798</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.002870414406061172</v>
+        <v>0.004851844627410173</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.1352840065956116</v>
+        <v>0.002363677602261305</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.08171200752258301</v>
+        <v>0.007085044868290424</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.005144533701241016</v>
+        <v>0.005139834247529507</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.08159405738115311</v>
+        <v>0.0009044002508744597</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.1708514839410782</v>
+        <v>0.002724980004131794</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.009263573214411736</v>
+        <v>0.006071652285754681</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.09871479868888855</v>
+        <v>0.002284699119627476</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.05713561922311783</v>
+        <v>0.001921304734423757</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.03266903758049011</v>
+        <v>0.003749715629965067</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.05211129784584045</v>
+        <v>0.001231833593919873</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.02024291269481182</v>
+        <v>0.001673050224781036</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.01067927666008472</v>
+        <v>0.009206089191138744</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.005377279594540596</v>
+        <v>0.00470312312245369</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.01778368279337883</v>
+        <v>0.00311655830591917</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.05825959146022797</v>
+        <v>0.006142067722976208</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.0560215450823307</v>
+        <v>5.285753286443651e-05</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.07601355016231537</v>
+        <v>0.000377240648958832</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.1184127777814865</v>
+        <v>0.01636292040348053</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.01959701627492905</v>
+        <v>0.001489499118179083</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.1075810045003891</v>
+        <v>0.0005285480292513967</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.3733243346214294</v>
+        <v>0.008690833114087582</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.1574293673038483</v>
+        <v>0.001595289679244161</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.001210764050483704</v>
+        <v>0.001312990672886372</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.0005675628781318665</v>
+        <v>0.003859501797705889</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.1074618250131607</v>
+        <v>0.0067061772570014</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.03640352189540863</v>
+        <v>0.0004726706829387695</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.04650304466485977</v>
+        <v>0.01580409146845341</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.02653205953538418</v>
+        <v>0.005087482742965221</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.07995927333831787</v>
+        <v>0.002110106172040105</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.118045948445797</v>
+        <v>0.01834786683320999</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.05985207110643387</v>
+        <v>0.002608858048915863</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.07391659170389175</v>
+        <v>0.001659959321841598</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.01646274887025356</v>
+        <v>0.005662614013999701</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.02688459120690823</v>
+        <v>0.0001224109437316656</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.03526924178004265</v>
+        <v>0.0016921745846048</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.01944616809487343</v>
+        <v>0.001874395762570202</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.04371058195829391</v>
+        <v>0.004371423274278641</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.08393068611621857</v>
+        <v>0.001711014425382018</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.03134135156869888</v>
+        <v>0.004826312884688377</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.01351713575422764</v>
+        <v>0.003709724172949791</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.04673189669847488</v>
+        <v>0.001771418494172394</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.08831438422203064</v>
+        <v>0.00664729718118906</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.1046549752354622</v>
+        <v>0.001352787483483553</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.08731599897146225</v>
+        <v>0.000114932656288147</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.1379473954439163</v>
+        <v>0.01805144548416138</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.02382417023181915</v>
+        <v>0.002039573155343533</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.1063645929098129</v>
+        <v>0.002631878945976496</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.1064787954092026</v>
+        <v>0.005425536539405584</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.008736412972211838</v>
+        <v>0.002877399325370789</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.05586868897080421</v>
+        <v>0.0028879523742944</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.04273073375225067</v>
+        <v>0.0001191602204926312</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.06344380229711533</v>
+        <v>0.001180359395220876</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.01166395097970963</v>
+        <v>0.0004477972397580743</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.01950310170650482</v>
+        <v>0.004910124000161886</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.01330580189824104</v>
+        <v>0.002455670852214098</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.07350870966911316</v>
+        <v>0.001246838713996112</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.06054389849305153</v>
+        <v>0.0002735707676038146</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.0697624459862709</v>
+        <v>0.002911417279392481</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.01717938855290413</v>
+        <v>0.0002770806895568967</v>
       </c>
       <c r="CK10" t="n">
-        <v>3.372691571712494e-05</v>
+        <v>0.001874247333034873</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.0118965320289135</v>
+        <v>3.752124030143023e-06</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.02882495522499084</v>
+        <v>7.653483044123277e-05</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.07396440207958221</v>
+        <v>0.00250119948759675</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.02157224342226982</v>
+        <v>1.88336125575006e-05</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.0981295257806778</v>
+        <v>0.006487286183983088</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.1792449355125427</v>
+        <v>0.01018570363521576</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.02385526895523071</v>
+        <v>0.001900816918350756</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.05285262316465378</v>
+        <v>0.001573329325765371</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.033943060785532</v>
+        <v>0.01042419113218784</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.01638950034976006</v>
+        <v>0.001100961118936539</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.01181018818169832</v>
+        <v>0.0006910572992637753</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.008080905303359032</v>
+        <v>0.004387615248560905</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.009059548377990723</v>
+        <v>0.002370976842939854</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.06042948737740517</v>
+        <v>0.0005898146773688495</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.07923152297735214</v>
+        <v>0.0009082605829462409</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.07751481235027313</v>
+        <v>0.002864202950149775</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.01938391476869583</v>
+        <v>3.94535600207746e-05</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.04226690530776978</v>
+        <v>0.0008162733283825219</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.02426087856292725</v>
+        <v>1.401691406499594e-05</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.06882862746715546</v>
+        <v>0.003707091324031353</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.1312515735626221</v>
+        <v>0.002402705606073141</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.02873318642377853</v>
+        <v>0.00152622174937278</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.1879904121160507</v>
+        <v>0.00561585882678628</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.3411277830600739</v>
+        <v>0.00982405710965395</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.2070213854312897</v>
+        <v>0.0008247485384345055</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.05971021577715874</v>
+        <v>0.001615266082808375</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.09650947153568268</v>
+        <v>0.001727273920550942</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.1310652494430542</v>
+        <v>0.01029970776289701</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.06921199709177017</v>
+        <v>0.001343678217381239</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.03059006109833717</v>
+        <v>0.00104816909879446</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.0335882380604744</v>
+        <v>0.001041415380313993</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.1652126312255859</v>
+        <v>0.001021562144160271</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.0007038074545562267</v>
+        <v>0.001277860603295267</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.04568776860833168</v>
+        <v>0.002499713096767664</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.03058597445487976</v>
+        <v>0.001276688766665757</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.02317536249756813</v>
+        <v>0.001253569265827537</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.04217897355556488</v>
+        <v>0.001952032558619976</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.05092039704322815</v>
+        <v>0.002115495735779405</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.04931553080677986</v>
+        <v>0.001137091661803424</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.06215467303991318</v>
+        <v>0.003795826807618141</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.06133819371461868</v>
+        <v>0.004324384033679962</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.04659856855869293</v>
+        <v>0.0001144073903560638</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.05154174566268921</v>
+        <v>0.001272327033802867</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.01697863452136517</v>
+        <v>0.0007547803106717765</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.1481193155050278</v>
+        <v>0.003716090694069862</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.0814923569560051</v>
+        <v>0.008366527035832405</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.03687009960412979</v>
+        <v>0.0001180043909698725</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.03355803340673447</v>
+        <v>0.002877818653360009</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.05173126980662346</v>
+        <v>2.339354250580072e-05</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.03931259363889694</v>
+        <v>0.0007229048060253263</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.08811970055103302</v>
+        <v>0.002263665199279785</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.08330881595611572</v>
+        <v>0.002285679802298546</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.02168301865458488</v>
+        <v>0.001871917629614472</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.008330652490258217</v>
+        <v>0.002326551359146833</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.007664009928703308</v>
+        <v>0.000815589795820415</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.0001759315637173131</v>
+        <v>0.002323987660929561</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.04433497786521912</v>
+        <v>0.004384872037917376</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.01109546422958374</v>
+        <v>0.000644567480776459</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.04133779928088188</v>
+        <v>0.001170128933154047</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.01830379851162434</v>
+        <v>0.002538105007261038</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.07864278554916382</v>
+        <v>0.006525278557091951</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.02801475860178471</v>
+        <v>0.003883257741108537</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.01059364527463913</v>
+        <v>0.001759388716891408</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.002884803339838982</v>
+        <v>0.004397723823785782</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.008326785638928413</v>
+        <v>7.100048242136836e-05</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.01515361666679382</v>
+        <v>0.005260493606328964</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.01187467016279697</v>
+        <v>0.001717282575555146</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.07827828824520111</v>
+        <v>0.00049835245590657</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.07343935966491699</v>
+        <v>0.0001139722298830748</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.07049860805273056</v>
+        <v>0.002541111316531897</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.008302913978695869</v>
+        <v>0.0001137923682108521</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.03765877336263657</v>
+        <v>0.0007800283492542803</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.005020244047045708</v>
+        <v>0.0008146989275701344</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.03182993084192276</v>
+        <v>0.0004969572764821351</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.04836858808994293</v>
+        <v>0.003842855570837855</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.05659164488315582</v>
+        <v>0.0009136810549534857</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.0122813917696476</v>
+        <v>0.001912666368298233</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.0401843786239624</v>
+        <v>0.00100682070478797</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.006499111652374268</v>
+        <v>0.003331075189635158</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.02171509340405464</v>
+        <v>8.299102773889899e-05</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.0650499016046524</v>
+        <v>0.002909106900915504</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.1024797186255455</v>
+        <v>0.0006364957080222666</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.03889228031039238</v>
+        <v>0.002078140852972865</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.05195017904043198</v>
+        <v>0.01082540117204189</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.11325503885746</v>
+        <v>0.01722109876573086</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.05544129014015198</v>
+        <v>0.002757491078227758</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.1484283804893494</v>
+        <v>0.003768058493733406</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.01044987142086029</v>
+        <v>0.00384322227910161</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.09051076322793961</v>
+        <v>0.003141731023788452</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.0796375572681427</v>
+        <v>0.003021710319444537</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.02190263941884041</v>
+        <v>0.00507775042206049</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.04243583977222443</v>
+        <v>0.003156871069222689</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.06585504859685898</v>
+        <v>0.004822788760066032</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.01535485684871674</v>
+        <v>0.0004443401703611016</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.05390511080622673</v>
+        <v>0.001389720709994435</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.2072794735431671</v>
+        <v>0.002813633996993303</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.004952344112098217</v>
+        <v>6.636924808844924e-05</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.09765831381082535</v>
+        <v>0.0004596881335601211</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.03123034164309502</v>
+        <v>0.003705983981490135</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.01346759684383869</v>
+        <v>0.001319055096246302</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.0002882994594983757</v>
+        <v>8.824544011076796e-07</v>
       </c>
       <c r="B11" t="n">
-        <v>0.002414235845208168</v>
+        <v>1.287002851313446e-05</v>
       </c>
       <c r="C11" t="n">
-        <v>9.450677316635847e-05</v>
+        <v>4.175605681666639e-06</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001315718982368708</v>
+        <v>2.754740307864267e-06</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0002965587773360312</v>
+        <v>2.964078248623991e-06</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0008198233554139733</v>
+        <v>1.017424619931262e-05</v>
       </c>
       <c r="G11" t="n">
-        <v>1.936909393407404e-05</v>
+        <v>1.207571358463611e-07</v>
       </c>
       <c r="H11" t="n">
-        <v>0.00108611339237541</v>
+        <v>5.361510829970939e-06</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0001373308041365817</v>
+        <v>1.231469241247396e-06</v>
       </c>
       <c r="J11" t="n">
-        <v>7.589737651869655e-05</v>
+        <v>1.049016077558917e-06</v>
       </c>
       <c r="K11" t="n">
-        <v>0.002033142140135169</v>
+        <v>1.65735837072134e-05</v>
       </c>
       <c r="L11" t="n">
-        <v>8.360471838386729e-05</v>
+        <v>6.346001555357361e-06</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0009866085601970553</v>
+        <v>5.634401077259099e-06</v>
       </c>
       <c r="N11" t="n">
-        <v>6.532522093039006e-05</v>
+        <v>3.447170911385911e-06</v>
       </c>
       <c r="O11" t="n">
-        <v>0.001118564046919346</v>
+        <v>1.006957245408557e-05</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0003324606805108488</v>
+        <v>1.122767912420386e-06</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0003458766150288284</v>
+        <v>3.673893615996349e-06</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0001014240260701627</v>
+        <v>1.489503802076797e-06</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0001648771722102538</v>
+        <v>6.427405878639547e-07</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0003387121832929552</v>
+        <v>1.479515617575089e-06</v>
       </c>
       <c r="U11" t="n">
-        <v>4.850974073633552e-05</v>
+        <v>3.143753133372229e-07</v>
       </c>
       <c r="V11" t="n">
-        <v>0.0002988993655890226</v>
+        <v>2.167539378206129e-06</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0002855330531019717</v>
+        <v>1.011650397231278e-06</v>
       </c>
       <c r="X11" t="n">
-        <v>8.392340532736853e-05</v>
+        <v>4.216964498482412e-06</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0001930580183397979</v>
+        <v>4.674028559747967e-07</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.0001939451904036105</v>
+        <v>2.078048510156805e-06</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.0002941074781119823</v>
+        <v>5.495064669958083e-08</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.0001487163972342387</v>
+        <v>1.061642933564144e-06</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.0003684732364490628</v>
+        <v>1.374337671222747e-06</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.0001703893503872678</v>
+        <v>7.148311169657973e-07</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.0002568238705862314</v>
+        <v>1.859917688307178e-06</v>
       </c>
       <c r="AF11" t="n">
-        <v>7.057009497657418e-06</v>
+        <v>3.167885552102234e-06</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.435110945953056e-05</v>
+        <v>2.280399257870158e-06</v>
       </c>
       <c r="AH11" t="n">
-        <v>7.619582902407274e-05</v>
+        <v>6.357401503009896e-07</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.0002283557987539098</v>
+        <v>5.425599738373421e-06</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.0001175752404378727</v>
+        <v>1.291836611017061e-06</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.0003567311214283109</v>
+        <v>1.400356609337905e-06</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.0003593777946662158</v>
+        <v>3.472307525953511e-06</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.629308644623961e-05</v>
+        <v>6.044846259101178e-07</v>
       </c>
       <c r="AN11" t="n">
-        <v>7.738326530670747e-05</v>
+        <v>2.358732217544457e-06</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.0001324865879723802</v>
+        <v>3.284839635853132e-07</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.0003119593602605164</v>
+        <v>2.205588771175826e-06</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.0001049740094458684</v>
+        <v>1.652522314543603e-07</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.0003004039172083139</v>
+        <v>2.920426823038724e-06</v>
       </c>
       <c r="AS11" t="n">
-        <v>9.512968244962394e-05</v>
+        <v>1.702822032711993e-06</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.0002146050392184407</v>
+        <v>2.073332325380761e-06</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.001607438316568732</v>
+        <v>1.592560147400945e-05</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.0001914437452796847</v>
+        <v>1.527903577880352e-06</v>
       </c>
       <c r="AW11" t="n">
-        <v>9.614793088985607e-05</v>
+        <v>2.695520379347727e-06</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.0001012975408229977</v>
+        <v>6.249751095310785e-06</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.0006441732402890921</v>
+        <v>9.209772542817518e-06</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4.343685577623546e-05</v>
+        <v>1.426068649834633e-07</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.0004670838243328035</v>
+        <v>1.462702357457601e-06</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.0001621444680495188</v>
+        <v>1.617726979930012e-06</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.0002564426395110786</v>
+        <v>6.402307235475746e-07</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.0003897461574524641</v>
+        <v>5.036539278080454e-06</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.0004575553175527602</v>
+        <v>2.672145456017461e-06</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.0003244603867642581</v>
+        <v>2.456856975641131e-07</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.0002536664833314717</v>
+        <v>3.602237711675116e-06</v>
       </c>
       <c r="BH11" t="n">
-        <v>5.035245339968242e-05</v>
+        <v>9.297752967540873e-07</v>
       </c>
       <c r="BI11" t="n">
-        <v>7.461859786417335e-05</v>
+        <v>1.867400897026528e-06</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.0001989781594602391</v>
+        <v>8.514728619957168e-07</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.0001156020589405671</v>
+        <v>1.554028358441428e-06</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.000157238362589851</v>
+        <v>8.078385462795268e-07</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.0002395060146227479</v>
+        <v>1.122758931160206e-06</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.0001844736543716863</v>
+        <v>1.137719209509669e-06</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.0001572287292219698</v>
+        <v>2.0643108200602e-07</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.0002525019226595759</v>
+        <v>9.389700039719173e-07</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.0001452516880817711</v>
+        <v>5.128604243509471e-07</v>
       </c>
       <c r="BR11" t="n">
-        <v>1.091157901100814e-05</v>
+        <v>5.585261533269659e-07</v>
       </c>
       <c r="BS11" t="n">
-        <v>2.186009078286588e-05</v>
+        <v>1.362172952212859e-08</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.0001856932940427214</v>
+        <v>1.21270738873136e-06</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.0001481944491388276</v>
+        <v>6.943583343854698e-07</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.000933852163143456</v>
+        <v>8.185673323168885e-06</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.0001815161958802491</v>
+        <v>7.854407044760592e-07</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.0001586041034897789</v>
+        <v>2.485582854205859e-06</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.094008621294051e-05</v>
+        <v>2.72605279860727e-06</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.0003810867783613503</v>
+        <v>6.669844424322946e-06</v>
       </c>
       <c r="CA11" t="n">
-        <v>9.531361138215289e-05</v>
+        <v>1.85389887974452e-06</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.0001782599429134279</v>
+        <v>1.653198978601722e-06</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.0002623872715048492</v>
+        <v>1.011627830393991e-07</v>
       </c>
       <c r="CD11" t="n">
-        <v>4.120108860661276e-05</v>
+        <v>1.801248572519398e-08</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.0004262422444298863</v>
+        <v>4.83182338939514e-06</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.0001637521345401183</v>
+        <v>9.807145033846609e-07</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.0002162939927075058</v>
+        <v>1.452840706406278e-06</v>
       </c>
       <c r="CH11" t="n">
-        <v>9.927205246640369e-05</v>
+        <v>3.285026650701184e-07</v>
       </c>
       <c r="CI11" t="n">
-        <v>9.701875387690961e-05</v>
+        <v>2.236461341453833e-06</v>
       </c>
       <c r="CJ11" t="n">
-        <v>7.601481775054708e-05</v>
+        <v>2.172484130369412e-07</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.0001860141201177612</v>
+        <v>1.290434056500089e-06</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.0001515437616035342</v>
+        <v>3.560739116892364e-07</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.0004080647486262023</v>
+        <v>1.436848492630816e-06</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.0001903949159896001</v>
+        <v>2.828131755450158e-06</v>
       </c>
       <c r="CO11" t="n">
-        <v>5.65074042242486e-05</v>
+        <v>2.780383738354431e-06</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.0003612103464547545</v>
+        <v>3.982466296292841e-06</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.0004894692683592439</v>
+        <v>4.832643298868788e-06</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.0002595253172330558</v>
+        <v>2.525115178286796e-06</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.0004086194094270468</v>
+        <v>3.529349328346143e-07</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.0004371898830868304</v>
+        <v>9.245730581142197e-08</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.0001438842882635072</v>
+        <v>1.280685637539136e-06</v>
       </c>
       <c r="CV11" t="n">
-        <v>3.164712325087748e-05</v>
+        <v>9.053799772118509e-07</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.000368686014553532</v>
+        <v>4.220588834868977e-06</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.0002046919398708269</v>
+        <v>1.469928520236863e-06</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.0003067740763071924</v>
+        <v>2.117205895046936e-06</v>
       </c>
       <c r="CZ11" t="n">
-        <v>9.379121183883399e-05</v>
+        <v>6.770237064301909e-07</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.0001349270751234144</v>
+        <v>2.661971393536078e-06</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.0001122065805247985</v>
+        <v>2.424071681161877e-07</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.0002787457779049873</v>
+        <v>9.847094588621985e-07</v>
       </c>
       <c r="DD11" t="n">
-        <v>9.368465543957427e-05</v>
+        <v>4.155338473310621e-08</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.0002053259668173268</v>
+        <v>2.514401558073587e-07</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.0003241387312300503</v>
+        <v>1.745751092130376e-06</v>
       </c>
       <c r="DG11" t="n">
-        <v>5.820272781420499e-05</v>
+        <v>1.302506234424072e-06</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.001022779382765293</v>
+        <v>6.463100135079003e-07</v>
       </c>
       <c r="DI11" t="n">
-        <v>6.877866690047085e-05</v>
+        <v>2.621970338623214e-07</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.13252060348168e-05</v>
+        <v>4.594605798047269e-06</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.0002159878640668467</v>
+        <v>1.211223320751742e-06</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.0004819104506168514</v>
+        <v>4.91398395752185e-06</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.0001386665389873087</v>
+        <v>1.631846089367173e-06</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.0001858624455053359</v>
+        <v>1.235162358170783e-06</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.0001684580929577351</v>
+        <v>1.264646130039182e-06</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.0001537600182928145</v>
+        <v>7.421457439704682e-07</v>
       </c>
       <c r="DQ11" t="n">
-        <v>5.378056084737182e-05</v>
+        <v>6.91599211677385e-07</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.0001836479495977983</v>
+        <v>1.005965145850496e-06</v>
       </c>
       <c r="DS11" t="n">
-        <v>5.716152008972131e-05</v>
+        <v>2.179644980060402e-06</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.0002144552563549951</v>
+        <v>1.603286364115775e-06</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.0001352396939182654</v>
+        <v>2.940563263109652e-06</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.0002974585513584316</v>
+        <v>6.374797294483869e-07</v>
       </c>
       <c r="DW11" t="n">
-        <v>1.883282720882562e-06</v>
+        <v>1.931145561684389e-06</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.0001265972387045622</v>
+        <v>2.452403805364156e-06</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.0002718616451602429</v>
+        <v>2.372108610870782e-06</v>
       </c>
       <c r="DZ11" t="n">
-        <v>1.948856515809894e-05</v>
+        <v>5.285572797220084e-07</v>
       </c>
       <c r="EA11" t="n">
-        <v>3.853419912047684e-06</v>
+        <v>2.977647682200768e-06</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.0002344074455322698</v>
+        <v>2.558068899816135e-06</v>
       </c>
       <c r="EC11" t="n">
-        <v>6.554724677698687e-05</v>
+        <v>2.111587491526734e-06</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.0001208224857691675</v>
+        <v>3.550956080289325e-06</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.0001819569442886859</v>
+        <v>2.717821871556225e-06</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.000193452084204182</v>
+        <v>9.944424164132215e-07</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.0003187627880834043</v>
+        <v>2.457594746374525e-06</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.0001674660597927868</v>
+        <v>5.201653721087496e-07</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.0001578228548169136</v>
+        <v>2.359016093578248e-07</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.0001797741570044309</v>
+        <v>6.068534617043042e-07</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.0001227262255270034</v>
+        <v>3.390802589819941e-07</v>
       </c>
       <c r="EL11" t="n">
-        <v>2.455746471241582e-05</v>
+        <v>4.811985832020582e-07</v>
       </c>
       <c r="EM11" t="n">
-        <v>3.766395457205363e-05</v>
+        <v>9.484001566306688e-07</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.0001206833621836267</v>
+        <v>5.047411377745448e-07</v>
       </c>
       <c r="EO11" t="n">
-        <v>6.792187195969746e-05</v>
+        <v>1.307109869230771e-06</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.000173380074556917</v>
+        <v>2.090939460686059e-06</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.0002328629343537614</v>
+        <v>4.649274956136651e-07</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.0001400799956172705</v>
+        <v>2.163431418011896e-06</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.0001128792864619754</v>
+        <v>1.504398142060381e-06</v>
       </c>
       <c r="ET11" t="n">
-        <v>1.364167292194907e-05</v>
+        <v>5.364925641515583e-07</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.0002197465219069272</v>
+        <v>2.447311260311835e-07</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.0006463491008616984</v>
+        <v>9.78433263298939e-07</v>
       </c>
       <c r="EW11" t="n">
-        <v>0.0003725145070347935</v>
+        <v>2.075522615996306e-06</v>
       </c>
       <c r="EX11" t="n">
-        <v>5.69774056202732e-05</v>
+        <v>9.743644113768823e-08</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.0003474769764579833</v>
+        <v>5.049389073974453e-06</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.0001240350829903036</v>
+        <v>1.099052951758495e-06</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.0002220204623881727</v>
+        <v>1.77800052370003e-06</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.000116642884677276</v>
+        <v>9.220894980899175e-08</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.000112548797915224</v>
+        <v>2.80311132883071e-06</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.0001628368918318301</v>
+        <v>3.62878921578158e-07</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.0001946634583873674</v>
+        <v>1.345374812444788e-06</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.0001390354882460088</v>
+        <v>3.755313571218721e-07</v>
       </c>
       <c r="FG11" t="n">
-        <v>3.761126208701171e-05</v>
+        <v>8.537090252502821e-07</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.0001294729736400768</v>
+        <v>3.31845603795955e-06</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.0003403234295547009</v>
+        <v>1.299962832490564e-06</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.0003561355406418443</v>
+        <v>1.528043753751263e-06</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.0001321785093750805</v>
+        <v>8.974632805802685e-07</v>
       </c>
       <c r="FL11" t="n">
-        <v>7.741033914498985e-05</v>
+        <v>2.17971046367893e-06</v>
       </c>
       <c r="FM11" t="n">
-        <v>2.298466097272467e-05</v>
+        <v>1.715239932309487e-07</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.0001979832450160757</v>
+        <v>4.019238986074924e-06</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.0001259880082216114</v>
+        <v>3.186857156833867e-06</v>
       </c>
       <c r="FP11" t="n">
-        <v>6.714851770084351e-05</v>
+        <v>3.580544216674753e-07</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.0003042524913325906</v>
+        <v>2.299830157426186e-06</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.0003315137582831085</v>
+        <v>2.640540515130851e-06</v>
       </c>
       <c r="FS11" t="n">
-        <v>7.634861685801297e-05</v>
+        <v>5.404633043326612e-07</v>
       </c>
       <c r="FT11" t="n">
-        <v>8.535687084076926e-05</v>
+        <v>3.443226432864321e-07</v>
       </c>
       <c r="FU11" t="n">
-        <v>5.119352863403037e-05</v>
+        <v>2.227619006589521e-06</v>
       </c>
       <c r="FV11" t="n">
-        <v>2.379529178142548e-06</v>
+        <v>3.969437329942593e-06</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.0001670422207098454</v>
+        <v>3.88504895454389e-06</v>
       </c>
       <c r="FX11" t="n">
-        <v>5.104943920741789e-05</v>
+        <v>3.396850161152543e-06</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.0002994289388880134</v>
+        <v>1.049525053531397e-06</v>
       </c>
       <c r="FZ11" t="n">
-        <v>8.677572623128071e-05</v>
+        <v>8.038181817937584e-07</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.0002333459124201909</v>
+        <v>3.590336291381391e-06</v>
       </c>
       <c r="GB11" t="n">
-        <v>8.366405381821096e-05</v>
+        <v>6.995417720645491e-07</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.0003999152395408601</v>
+        <v>3.977551841671811e-06</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.0002463759446982294</v>
+        <v>2.33255855164316e-06</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.001051922328770161</v>
+        <v>1.649021896810154e-06</v>
       </c>
       <c r="GF11" t="n">
-        <v>3.458152423263527e-05</v>
+        <v>1.396955440213787e-06</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.0004176950315013528</v>
+        <v>1.112312702389318e-06</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.3215585649013519</v>
+        <v>0.2723498940467834</v>
       </c>
       <c r="B12" t="n">
-        <v>3.441300868988037</v>
+        <v>2.870011329650879</v>
       </c>
       <c r="C12" t="n">
-        <v>0.528874933719635</v>
+        <v>1.149889707565308</v>
       </c>
       <c r="D12" t="n">
-        <v>2.213431119918823</v>
+        <v>1.985829949378967</v>
       </c>
       <c r="E12" t="n">
-        <v>2.135538339614868</v>
+        <v>0.7244842052459717</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4869743585586548</v>
+        <v>1.993994951248169</v>
       </c>
       <c r="G12" t="n">
-        <v>0.749772846698761</v>
+        <v>0.6032795906066895</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4339165985584259</v>
+        <v>0.4644029140472412</v>
       </c>
       <c r="I12" t="n">
-        <v>0.03021512925624847</v>
+        <v>0.01026461273431778</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2139988988637924</v>
+        <v>0.1595449447631836</v>
       </c>
       <c r="K12" t="n">
-        <v>2.610986948013306</v>
+        <v>3.009194850921631</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1257594078779221</v>
+        <v>1.759315729141235</v>
       </c>
       <c r="M12" t="n">
-        <v>1.459911942481995</v>
+        <v>2.740686416625977</v>
       </c>
       <c r="N12" t="n">
-        <v>1.964255928993225</v>
+        <v>0.1953449249267578</v>
       </c>
       <c r="O12" t="n">
-        <v>0.566487729549408</v>
+        <v>1.533650040626526</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9133554100990295</v>
+        <v>0.3813099265098572</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.2019776701927185</v>
+        <v>0.3664056360721588</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1200258284807205</v>
+        <v>0.3603065013885498</v>
       </c>
       <c r="S12" t="n">
-        <v>0.004449004307389259</v>
+        <v>0.001513183116912842</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5985603928565979</v>
+        <v>0.05036453157663345</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1026110425591469</v>
+        <v>0.1796585321426392</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3536320328712463</v>
+        <v>0.03740088269114494</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1320252269506454</v>
+        <v>0.1325908601284027</v>
       </c>
       <c r="X12" t="n">
-        <v>0.5026675462722778</v>
+        <v>1.11268150806427</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.4394773244857788</v>
+        <v>0.07239474356174469</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.3684418499469757</v>
+        <v>0.03378560766577721</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.4423376619815826</v>
+        <v>0.3762539625167847</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.1963031888008118</v>
+        <v>0.5183650851249695</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.4454294145107269</v>
+        <v>0.8783751130104065</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.001558423042297363</v>
+        <v>0.1079970002174377</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.2099548727273941</v>
+        <v>0.7169889211654663</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.25223308801651</v>
+        <v>1.146064400672913</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.1170714721083641</v>
+        <v>1.123582005500793</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.3377853631973267</v>
+        <v>0.3421652317047119</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.2451923787593842</v>
+        <v>0.01319069974124432</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.2992213368415833</v>
+        <v>0.2805559635162354</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.1939163655042648</v>
+        <v>0.09107277542352676</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.6704769730567932</v>
+        <v>0.7312968373298645</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.01467826589941978</v>
+        <v>0.609649658203125</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.08151017129421234</v>
+        <v>0.7467702627182007</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.05044166743755341</v>
+        <v>0.6620683073997498</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.3930818438529968</v>
+        <v>0.9066131114959717</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.1581360399723053</v>
+        <v>0.3146669268608093</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.01215846464037895</v>
+        <v>0.1871788501739502</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.2428881973028183</v>
+        <v>0.364462286233902</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.221690446138382</v>
+        <v>0.06454357504844666</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.222702741622925</v>
+        <v>1.596806764602661</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.3239164650440216</v>
+        <v>0.3282117247581482</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.727095901966095</v>
+        <v>1.405861735343933</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.9240482449531555</v>
+        <v>1.019784331321716</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.5162045359611511</v>
+        <v>1.152092933654785</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.123684324324131</v>
+        <v>0.05552258715033531</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.0616433247923851</v>
+        <v>0.09273140132427216</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.194864422082901</v>
+        <v>0.480783075094223</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.1559788882732391</v>
+        <v>0.0915757417678833</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.4732913374900818</v>
+        <v>0.4375457763671875</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.3960175216197968</v>
+        <v>0.7401732802391052</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.6393992304801941</v>
+        <v>0.2738246917724609</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.359655737876892</v>
+        <v>0.986373245716095</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.2199304848909378</v>
+        <v>0.1301944851875305</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.5761827826499939</v>
+        <v>0.2302245646715164</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.4235074818134308</v>
+        <v>0.08154650032520294</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.1685723066329956</v>
+        <v>0.4294480979442596</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.2689321339130402</v>
+        <v>0.1355457156896591</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.5075494647026062</v>
+        <v>0.08907313644886017</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.2157161980867386</v>
+        <v>0.169879674911499</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.08131561428308487</v>
+        <v>0.1318977177143097</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.02465623617172241</v>
+        <v>0.006157012656331062</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.2921834588050842</v>
+        <v>0.319945365190506</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.04102678969502449</v>
+        <v>0.1381594836711884</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.2207917273044586</v>
+        <v>0.3892406523227692</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.0885702520608902</v>
+        <v>0.2229650169610977</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.2157591581344604</v>
+        <v>0.1173997074365616</v>
       </c>
       <c r="BV12" t="n">
-        <v>1.452400326728821</v>
+        <v>0.3474968075752258</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.6176008582115173</v>
+        <v>0.4690376222133636</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.2705165147781372</v>
+        <v>0.7979443669319153</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.6364834904670715</v>
+        <v>0.446966141462326</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.2447259277105331</v>
+        <v>1.247984409332275</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.159347265958786</v>
+        <v>0.001836095005273819</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.02607123181223869</v>
+        <v>0.107666052877903</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.3986836075782776</v>
+        <v>0.2266629934310913</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.07155205309391022</v>
+        <v>0.02098860032856464</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.5450722575187683</v>
+        <v>0.9407604932785034</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.1583328098058701</v>
+        <v>0.3329645991325378</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.3818470537662506</v>
+        <v>0.7665609121322632</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.1889289915561676</v>
+        <v>0.2235608100891113</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.2404663413763046</v>
+        <v>0.3314691483974457</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.1152911335229874</v>
+        <v>0.0106993205845356</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.06569521874189377</v>
+        <v>0.3316384553909302</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.2582741379737854</v>
+        <v>0.04090097546577454</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.4207088649272919</v>
+        <v>0.02660313248634338</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.002686150604858994</v>
+        <v>0.3425833880901337</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.01030020043253899</v>
+        <v>1.084735155105591</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.0617157407104969</v>
+        <v>0.9485167264938354</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.1632850170135498</v>
+        <v>0.4020046889781952</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.1213807687163353</v>
+        <v>0.1518339961767197</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.6822362542152405</v>
+        <v>0.1737683117389679</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.6523936986923218</v>
+        <v>0.6383627653121948</v>
       </c>
       <c r="CU12" t="n">
-        <v>0.01007788628339767</v>
+        <v>0.1139917299151421</v>
       </c>
       <c r="CV12" t="n">
-        <v>0.09010380506515503</v>
+        <v>0.02947256900370121</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.4423431158065796</v>
+        <v>0.8677370548248291</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.2577391266822815</v>
+        <v>0.4003269672393799</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.5083239674568176</v>
+        <v>0.7682955861091614</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.08791446685791016</v>
+        <v>0.01611751690506935</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.3953527808189392</v>
+        <v>0.3525997698307037</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.05516044422984123</v>
+        <v>0.04301460459828377</v>
       </c>
       <c r="DC12" t="n">
-        <v>0.07060040533542633</v>
+        <v>0.3846656382083893</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.1471536159515381</v>
+        <v>0.01979636028409004</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.003037318587303162</v>
+        <v>0.3110041618347168</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.6074503660202026</v>
+        <v>0.9535706043243408</v>
       </c>
       <c r="DG12" t="n">
-        <v>0.2410244047641754</v>
+        <v>0.0009267926216125488</v>
       </c>
       <c r="DH12" t="n">
-        <v>1.35052478313446</v>
+        <v>0.3355355560779572</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.298189252614975</v>
+        <v>0.6473127007484436</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.1408703476190567</v>
+        <v>1.075919985771179</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.5839849710464478</v>
+        <v>0.01455364376306534</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.5753165483474731</v>
+        <v>1.704203367233276</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.3650451600551605</v>
+        <v>0.2424448430538177</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.2011033296585083</v>
+        <v>0.2714160084724426</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.3281565010547638</v>
+        <v>0.1659429222345352</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.1950522214174271</v>
+        <v>0.450370728969574</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.04939974844455719</v>
+        <v>0.5222442150115967</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.0548018179833889</v>
+        <v>0.3830376863479614</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.2223034799098969</v>
+        <v>0.3682824373245239</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.2738100290298462</v>
+        <v>0.1974466741085052</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.1616463959217072</v>
+        <v>0.3298087418079376</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.3035854399204254</v>
+        <v>0.8766249418258667</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.1390139907598495</v>
+        <v>0.255527526140213</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.008994419127702713</v>
+        <v>0.3233582973480225</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.5663718581199646</v>
+        <v>0.6346644163131714</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.1183618158102036</v>
+        <v>0.06206856667995453</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.343718558549881</v>
+        <v>0.4428062438964844</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.1898131221532822</v>
+        <v>0.33343106508255</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.06474490463733673</v>
+        <v>0.03342466056346893</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.224742203950882</v>
+        <v>1.309455037117004</v>
       </c>
       <c r="EE12" t="n">
-        <v>0.04442061483860016</v>
+        <v>0.9519147872924805</v>
       </c>
       <c r="EF12" t="n">
-        <v>0.1956298500299454</v>
+        <v>0.05975469946861267</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.3469268977642059</v>
+        <v>1.054585576057434</v>
       </c>
       <c r="EH12" t="n">
-        <v>0.2706073224544525</v>
+        <v>0.2029446959495544</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.2247915267944336</v>
+        <v>0.615559995174408</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.3968444466590881</v>
+        <v>0.02103065699338913</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.1657559424638748</v>
+        <v>0.2203602194786072</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.110916867852211</v>
+        <v>0.006546482443809509</v>
       </c>
       <c r="EM12" t="n">
-        <v>0.02144358493387699</v>
+        <v>0.1786125898361206</v>
       </c>
       <c r="EN12" t="n">
-        <v>0.06638018786907196</v>
+        <v>0.124628871679306</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.01827371120452881</v>
+        <v>0.06482607126235962</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.1312337219715118</v>
+        <v>0.4475618898868561</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.2874685823917389</v>
+        <v>0.1029204875230789</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.4784810245037079</v>
+        <v>0.4909976720809937</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.2083879858255386</v>
+        <v>0.03232962265610695</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.4881473183631897</v>
+        <v>0.4231685996055603</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.001839149743318558</v>
+        <v>0.3898770809173584</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.3413088023662567</v>
+        <v>0.3905183076858521</v>
       </c>
       <c r="EW12" t="n">
-        <v>0.1096019446849823</v>
+        <v>0.4963121712207794</v>
       </c>
       <c r="EX12" t="n">
-        <v>0.00912654772400856</v>
+        <v>0.01284001115709543</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.4283450245857239</v>
+        <v>1.057952284812927</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0.1533181220293045</v>
+        <v>0.3788591325283051</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.5285540223121643</v>
+        <v>0.8550463318824768</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.04931790381669998</v>
+        <v>0.2267286628484726</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.2903827130794525</v>
+        <v>0.4540614485740662</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.1455889791250229</v>
+        <v>0.05579293519258499</v>
       </c>
       <c r="FE12" t="n">
-        <v>0.08435500413179398</v>
+        <v>0.4274773597717285</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.2966054379940033</v>
+        <v>0.04234045743942261</v>
       </c>
       <c r="FG12" t="n">
-        <v>0.1367595791816711</v>
+        <v>0.0692923367023468</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.3497430682182312</v>
+        <v>0.5656042098999023</v>
       </c>
       <c r="FI12" t="n">
-        <v>0.2712946236133575</v>
+        <v>0.09722405672073364</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.5463405251502991</v>
+        <v>0.5000590682029724</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.07076166570186615</v>
+        <v>0.6229056119918823</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.3553842902183533</v>
+        <v>0.629880428314209</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.06670668721199036</v>
+        <v>0.1505605727434158</v>
       </c>
       <c r="FN12" t="n">
-        <v>0.1896360069513321</v>
+        <v>0.1458125114440918</v>
       </c>
       <c r="FO12" t="n">
-        <v>0.2109883427619934</v>
+        <v>0.03625793755054474</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.2553529143333435</v>
+        <v>0.1598405390977859</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.3368143439292908</v>
+        <v>0.6250962018966675</v>
       </c>
       <c r="FR12" t="n">
-        <v>0.01279488019645214</v>
+        <v>0.732490062713623</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.5530776977539062</v>
+        <v>0.3106393814086914</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.2380808144807816</v>
+        <v>0.2778668105602264</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.1847616285085678</v>
+        <v>0.3120477795600891</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.1495171636343002</v>
+        <v>0.04487399756908417</v>
       </c>
       <c r="FW12" t="n">
-        <v>0.296306699514389</v>
+        <v>0.3156873285770416</v>
       </c>
       <c r="FX12" t="n">
-        <v>0.1624579429626465</v>
+        <v>0.7546083331108093</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.4089345335960388</v>
+        <v>0.07672648131847382</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.1194399893283844</v>
+        <v>0.3935374617576599</v>
       </c>
       <c r="GA12" t="n">
-        <v>0.164684846997261</v>
+        <v>0.5575827360153198</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.3029879629611969</v>
+        <v>0.2690765857696533</v>
       </c>
       <c r="GC12" t="n">
-        <v>0.3115698993206024</v>
+        <v>0.09463165700435638</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.4478906095027924</v>
+        <v>0.3331604599952698</v>
       </c>
       <c r="GE12" t="n">
-        <v>1.162730574607849</v>
+        <v>0.6708000302314758</v>
       </c>
       <c r="GF12" t="n">
-        <v>0.06132059544324875</v>
+        <v>0.2904472053050995</v>
       </c>
       <c r="GG12" t="n">
-        <v>0.09003313630819321</v>
+        <v>0.08552562445402145</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.8515565395355225</v>
+        <v>0.2259873002767563</v>
       </c>
       <c r="B13" t="n">
-        <v>5.957437515258789</v>
+        <v>1.072929739952087</v>
       </c>
       <c r="C13" t="n">
-        <v>0.382714569568634</v>
+        <v>0.2507728934288025</v>
       </c>
       <c r="D13" t="n">
-        <v>2.916254281997681</v>
+        <v>0.4292021989822388</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6782180070877075</v>
+        <v>0.6200361251831055</v>
       </c>
       <c r="F13" t="n">
-        <v>4.456031799316406</v>
+        <v>1.103110551834106</v>
       </c>
       <c r="G13" t="n">
-        <v>0.244693398475647</v>
+        <v>0.4311277866363525</v>
       </c>
       <c r="H13" t="n">
-        <v>2.193047046661377</v>
+        <v>1.523959994316101</v>
       </c>
       <c r="I13" t="n">
-        <v>0.02398763224482536</v>
+        <v>0.5477795004844666</v>
       </c>
       <c r="J13" t="n">
-        <v>1.437668085098267</v>
+        <v>0.07122841477394104</v>
       </c>
       <c r="K13" t="n">
-        <v>5.073957920074463</v>
+        <v>1.244004130363464</v>
       </c>
       <c r="L13" t="n">
-        <v>0.203101858496666</v>
+        <v>0.5027683973312378</v>
       </c>
       <c r="M13" t="n">
-        <v>2.389401435852051</v>
+        <v>0.7170444130897522</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2606657147407532</v>
+        <v>1.521110415458679</v>
       </c>
       <c r="O13" t="n">
-        <v>4.208368301391602</v>
+        <v>1.323276996612549</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3931884169578552</v>
+        <v>0.3695961833000183</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.5137224197387695</v>
+        <v>1.324479579925537</v>
       </c>
       <c r="R13" t="n">
-        <v>0.1630980670452118</v>
+        <v>0.7102482318878174</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1264360547065735</v>
+        <v>0.3462162911891937</v>
       </c>
       <c r="T13" t="n">
-        <v>0.301021546125412</v>
+        <v>0.2407456934452057</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4006927013397217</v>
+        <v>0.08399835228919983</v>
       </c>
       <c r="V13" t="n">
-        <v>0.5920504927635193</v>
+        <v>0.4585054218769073</v>
       </c>
       <c r="W13" t="n">
-        <v>0.8337922096252441</v>
+        <v>0.3388855755329132</v>
       </c>
       <c r="X13" t="n">
-        <v>0.5535549521446228</v>
+        <v>0.09375286102294922</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.5419770479202271</v>
+        <v>0.1414180845022202</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.722933828830719</v>
+        <v>0.05884057655930519</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.9091038107872009</v>
+        <v>0.04365216940641403</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.00706171989440918</v>
+        <v>0.1949048340320587</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.3024779558181763</v>
+        <v>0.3603087663650513</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.1551077663898468</v>
+        <v>0.03170932829380035</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.3758100867271423</v>
+        <v>0.3361466228961945</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.2329671084880829</v>
+        <v>0.3031573891639709</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.03036792203783989</v>
+        <v>0.2521654665470123</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.3312402963638306</v>
+        <v>0.06398723274469376</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.36224165558815</v>
+        <v>0.3035896718502045</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.263164609670639</v>
+        <v>0.2644306123256683</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.3980762362480164</v>
+        <v>0.4842644929885864</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.8190439343452454</v>
+        <v>0.4027330577373505</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.1113075315952301</v>
+        <v>0.1579522043466568</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.3049560189247131</v>
+        <v>0.002973999828100204</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.7672514915466309</v>
+        <v>0.2358593046665192</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.8634297847747803</v>
+        <v>0.2262879610061646</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.1172007992863655</v>
+        <v>0.1818191707134247</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.2315041720867157</v>
+        <v>0.2152729034423828</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.6311396360397339</v>
+        <v>0.006531756371259689</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.336045891046524</v>
+        <v>0.08052590489387512</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.486191987991333</v>
+        <v>2.366540431976318</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.138846680521965</v>
+        <v>0.02388855069875717</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.010528683662415</v>
+        <v>0.1965591311454773</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.05221991240978241</v>
+        <v>0.1322955042123795</v>
       </c>
       <c r="AY13" t="n">
-        <v>2.433576345443726</v>
+        <v>0.8330973386764526</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.6497651338577271</v>
+        <v>0.03453237935900688</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.082223296165466</v>
+        <v>0.4529836177825928</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.340724945068359</v>
+        <v>0.1962478905916214</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.6906337141990662</v>
+        <v>0.1019684299826622</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.9816325902938843</v>
+        <v>1.03049111366272</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.9820474982261658</v>
+        <v>0.1824261844158173</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.7397320866584778</v>
+        <v>0.2460818141698837</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.255112171173096</v>
+        <v>0.4589349329471588</v>
       </c>
       <c r="BH13" t="n">
-        <v>1.006279945373535</v>
+        <v>0.04417820274829865</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.6263569593429565</v>
+        <v>0.145698755979538</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.5703977346420288</v>
+        <v>0.6089605093002319</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.03375008702278137</v>
+        <v>0.1556539535522461</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.2004711478948593</v>
+        <v>0.0106632262468338</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.6412556171417236</v>
+        <v>0.3692987561225891</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.01459035277366638</v>
+        <v>0.5214965343475342</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.3945397436618805</v>
+        <v>0.1416481584310532</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.2662680745124817</v>
+        <v>0.3777816593647003</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.1126145422458649</v>
+        <v>0.1837624162435532</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.3527207970619202</v>
+        <v>0.2851917743682861</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.4219496250152588</v>
+        <v>0.03778663650155067</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.1176548600196838</v>
+        <v>0.03624409437179565</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.2043114006519318</v>
+        <v>0.275754988193512</v>
       </c>
       <c r="BV13" t="n">
-        <v>1.825523018836975</v>
+        <v>0.8606627583503723</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.5894112586975098</v>
+        <v>0.05261010676622391</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.4978958964347839</v>
+        <v>0.2890788018703461</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.4205718040466309</v>
+        <v>0.3683103322982788</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1.153667569160461</v>
+        <v>0.4053036272525787</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.04220028221607208</v>
+        <v>0.4009160697460175</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.4481426477432251</v>
+        <v>0.2875750362873077</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.8590883612632751</v>
+        <v>0.06419401615858078</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.1328786313533783</v>
+        <v>0.1055917665362358</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.9392749071121216</v>
+        <v>0.3465909361839294</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.4817326068878174</v>
+        <v>0.1739953458309174</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.4976716935634613</v>
+        <v>0.06370460242033005</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.04162615910172462</v>
+        <v>0.2270143181085587</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.7068886756896973</v>
+        <v>0.2761453092098236</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.3864396810531616</v>
+        <v>0.0726621001958847</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.4536856412887573</v>
+        <v>0.06031031161546707</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.5932176113128662</v>
+        <v>0.04404032975435257</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.6701197028160095</v>
+        <v>0.4559778869152069</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.1850819885730743</v>
+        <v>0.3579855561256409</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.03198786452412605</v>
+        <v>0.1469855457544327</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.2275202870368958</v>
+        <v>0.4711311757564545</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.2344545125961304</v>
+        <v>0.2846174240112305</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.2767913341522217</v>
+        <v>0.1392342299222946</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.9099722504615784</v>
+        <v>0.05049468576908112</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.710018515586853</v>
+        <v>0.3393748700618744</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.0184362381696701</v>
+        <v>0.03423883020877838</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.04910299181938171</v>
+        <v>0.2026598304510117</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.848389744758606</v>
+        <v>0.3126296401023865</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.4650988876819611</v>
+        <v>0.1743877381086349</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.6978020668029785</v>
+        <v>0.1302590519189835</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.1398966312408447</v>
+        <v>0.2486609220504761</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.8760873675346375</v>
+        <v>0.3473071157932281</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.3451689481735229</v>
+        <v>0.01066905912011862</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.6388010382652283</v>
+        <v>0.0270036943256855</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.3975589275360107</v>
+        <v>0.05908331647515297</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.2017704248428345</v>
+        <v>0.01346822828054428</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.6906677484512329</v>
+        <v>0.3068786859512329</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.1119575574994087</v>
+        <v>0.157551109790802</v>
       </c>
       <c r="DH13" t="n">
-        <v>2.26693058013916</v>
+        <v>0.1050515919923782</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.6471169590950012</v>
+        <v>0.3581028580665588</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.5850987434387207</v>
+        <v>0.4871155619621277</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.4956351220607758</v>
+        <v>0.08670160174369812</v>
       </c>
       <c r="DL13" t="n">
-        <v>1.301858186721802</v>
+        <v>0.1666724383831024</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.5578177571296692</v>
+        <v>0.1904822289943695</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.0717909187078476</v>
+        <v>0.3227944672107697</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.2930676341056824</v>
+        <v>0.3103605210781097</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.06640100479125977</v>
+        <v>0.11665428429842</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.05175259709358215</v>
+        <v>0.04756264388561249</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.04063555225729942</v>
+        <v>0.4011166989803314</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.3643921613693237</v>
+        <v>0.1856446266174316</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.6852759718894958</v>
+        <v>0.1928386986255646</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.06277363002300262</v>
+        <v>0.1601757705211639</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.7204563021659851</v>
+        <v>0.4941393136978149</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.1653701812028885</v>
+        <v>0.2511123418807983</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.07029958814382553</v>
+        <v>0.5309451818466187</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.5114501714706421</v>
+        <v>0.3123579621315002</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.1504464000463486</v>
+        <v>0.06803832948207855</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.07242026180028915</v>
+        <v>0.2360826730728149</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.4878382086753845</v>
+        <v>0.0550248883664608</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.1346953809261322</v>
+        <v>0.1356472074985504</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.1882276833057404</v>
+        <v>0.2547158896923065</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.5914680957794189</v>
+        <v>0.2319583296775818</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.2774895429611206</v>
+        <v>0.04894570633769035</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.8786633014678955</v>
+        <v>0.2349621653556824</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.3459628820419312</v>
+        <v>0.1176113039255142</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.03346467018127441</v>
+        <v>0.1443785727024078</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.394670158624649</v>
+        <v>0.3916825950145721</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.4420825839042664</v>
+        <v>0.06961333751678467</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.4089283347129822</v>
+        <v>0.03176137432456017</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.2715941667556763</v>
+        <v>0.1599403917789459</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.2174731492996216</v>
+        <v>0.01923226565122604</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.06519272923469543</v>
+        <v>0.1645174920558929</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.6028991341590881</v>
+        <v>0.2965400516986847</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.5401257276535034</v>
+        <v>0.1474324017763138</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.5698126554489136</v>
+        <v>0.1238169223070145</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.7541537284851074</v>
+        <v>0.197269931435585</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.4766553342342377</v>
+        <v>0.3880434334278107</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.3792552351951599</v>
+        <v>0.03526406735181808</v>
       </c>
       <c r="EV13" t="n">
-        <v>1.31359589099884</v>
+        <v>0.01579354330897331</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.3189603090286255</v>
+        <v>0.276881217956543</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.03208588063716888</v>
+        <v>0.1710976958274841</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.7750863432884216</v>
+        <v>0.3983840048313141</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.3417181968688965</v>
+        <v>0.1186853051185608</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.5880992412567139</v>
+        <v>0.1460286676883698</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.2009845823049545</v>
+        <v>0.182469055056572</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.6279723048210144</v>
+        <v>0.3240120112895966</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.6003824472427368</v>
+        <v>0.1024338603019714</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.466724693775177</v>
+        <v>0.05716317892074585</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.6011257767677307</v>
+        <v>0.01777830719947815</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.1589974761009216</v>
+        <v>0.04606451466679573</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.4860472679138184</v>
+        <v>0.1666807681322098</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.2140242457389832</v>
+        <v>0.2229872941970825</v>
       </c>
       <c r="FJ13" t="n">
-        <v>1.110485553741455</v>
+        <v>0.2941869497299194</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.5998097062110901</v>
+        <v>0.000245717354118824</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.2587460279464722</v>
+        <v>0.274494856595993</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.165667712688446</v>
+        <v>0.2010384649038315</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.2989199161529541</v>
+        <v>0.1675480008125305</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.38632532954216</v>
+        <v>0.5097719430923462</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.387887716293335</v>
+        <v>0.090973861515522</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.9542347192764282</v>
+        <v>0.04871644824743271</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.6659740805625916</v>
+        <v>0.2312428504228592</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.4820132553577423</v>
+        <v>0.4431984126567841</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.4298547208309174</v>
+        <v>0.5322392582893372</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.09277421236038208</v>
+        <v>0.1089771017432213</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.4153920114040375</v>
+        <v>0.3013745546340942</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.3093442320823669</v>
+        <v>0.5115548372268677</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.6105672717094421</v>
+        <v>0.4609749019145966</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.7163317203521729</v>
+        <v>0.0735960453748703</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.1777236014604568</v>
+        <v>0.0483592301607132</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.6444494128227234</v>
+        <v>0.2745076417922974</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.2472275197505951</v>
+        <v>0.1294501721858978</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.9969771504402161</v>
+        <v>0.2403471618890762</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.2884360551834106</v>
+        <v>0.07234014570713043</v>
       </c>
       <c r="GE13" t="n">
-        <v>2.221816301345825</v>
+        <v>0.1870428919792175</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.009759999811649323</v>
+        <v>0.05450072884559631</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.5213454961776733</v>
+        <v>0.04306740313768387</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.002030198462307453</v>
+        <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1100059747695923</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0.003481960855424404</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1353030651807785</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0438297763466835</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.02525205537676811</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.03449894487857819</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.005726469680666924</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0.02082560397684574</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.02061675861477852</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1032796427607536</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01330838166177273</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1038581132888794</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0.03319040685892105</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0173824205994606</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0.02462871745228767</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.01029525324702263</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.02352836728096008</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.01493002939969301</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.01473039016127586</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0.01190476585179567</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0262987744063139</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.01116537488996983</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.004734035581350327</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.005320116877555847</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.01354661397635937</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.0105626629665494</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.004591736011207104</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.008344339206814766</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.01266609225422144</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.01933865435421467</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.007527054287493229</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.002316536149010062</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.00794095266610384</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.001134730409830809</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.02027194015681744</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.0002319337800145149</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.02429093234241009</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.006086595356464386</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.002362600993365049</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.006519549526274204</v>
+        <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.007853077724575996</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.002749991603195667</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.003165732137858868</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.01127747260034084</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.01692830957472324</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.05132901668548584</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.009232917800545692</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.07637393474578857</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.05138205364346504</v>
+        <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.03350881487131119</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.007462549023330212</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.003438983112573624</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.02519845776259899</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.007953298278152943</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.02914704941213131</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.008914772421121597</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.03425395861268044</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.0280443225055933</v>
+        <v>0</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.02262848615646362</v>
+        <v>0</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.01579943671822548</v>
+        <v>0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.0169753935188055</v>
+        <v>0</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.001213987590745091</v>
+        <v>0</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.007464312016963959</v>
+        <v>0</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.001342191593721509</v>
+        <v>0</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.002703696256503463</v>
+        <v>0</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.006798337679356337</v>
+        <v>0</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.009157581254839897</v>
+        <v>0</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.006681264843791723</v>
+        <v>0</v>
       </c>
       <c r="BR14" t="n">
-        <v>0.008690927177667618</v>
+        <v>0</v>
       </c>
       <c r="BS14" t="n">
-        <v>0.02204956859350204</v>
+        <v>0</v>
       </c>
       <c r="BT14" t="n">
-        <v>0.008034886792302132</v>
+        <v>0</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.02541441842913628</v>
+        <v>0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.02977613173425198</v>
+        <v>0</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.01212474144995213</v>
+        <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.04062278568744659</v>
+        <v>0</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.01788683049380779</v>
+        <v>0</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.009056512266397476</v>
+        <v>0</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.003994356840848923</v>
+        <v>0</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.001381514826789498</v>
+        <v>0</v>
       </c>
       <c r="CC14" t="n">
-        <v>0.01943506672978401</v>
+        <v>0</v>
       </c>
       <c r="CD14" t="n">
-        <v>0.0002416695933789015</v>
+        <v>0</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.01237535290420055</v>
+        <v>0</v>
       </c>
       <c r="CF14" t="n">
-        <v>0.01141024474054575</v>
+        <v>0</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.02766749449074268</v>
+        <v>0</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.00774636073037982</v>
+        <v>0</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.01038448326289654</v>
+        <v>0</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.731107477098703e-05</v>
+        <v>0</v>
       </c>
       <c r="CK14" t="n">
-        <v>0.003178224666044116</v>
+        <v>0</v>
       </c>
       <c r="CL14" t="n">
-        <v>0.01063029933720827</v>
+        <v>0</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.0208157766610384</v>
+        <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.01457643415778875</v>
+        <v>0</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.00416877493262291</v>
+        <v>0</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.02764153108000755</v>
+        <v>0</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.01850565709173679</v>
+        <v>0</v>
       </c>
       <c r="CR14" t="n">
-        <v>0.003415492130443454</v>
+        <v>0</v>
       </c>
       <c r="CS14" t="n">
-        <v>0.02874134108424187</v>
+        <v>0</v>
       </c>
       <c r="CT14" t="n">
-        <v>0.01439549494534731</v>
+        <v>0</v>
       </c>
       <c r="CU14" t="n">
-        <v>0.02275760844349861</v>
+        <v>0</v>
       </c>
       <c r="CV14" t="n">
-        <v>0.001010644831694663</v>
+        <v>0</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.01326397527009249</v>
+        <v>0</v>
       </c>
       <c r="CX14" t="n">
-        <v>0.01640773564577103</v>
+        <v>0</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.02725416235625744</v>
+        <v>0</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.008686527609825134</v>
+        <v>0</v>
       </c>
       <c r="DA14" t="n">
-        <v>0.01221188437193632</v>
+        <v>0</v>
       </c>
       <c r="DB14" t="n">
-        <v>0.0008054429199546576</v>
+        <v>0</v>
       </c>
       <c r="DC14" t="n">
-        <v>0.005915905814617872</v>
+        <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>0.006004843395203352</v>
+        <v>0</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.009341499768197536</v>
+        <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.02166286483407021</v>
+        <v>0</v>
       </c>
       <c r="DG14" t="n">
-        <v>0.02906651236116886</v>
+        <v>0</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.03646950051188469</v>
+        <v>0</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.002537489170208573</v>
+        <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0.005746510811150074</v>
+        <v>0</v>
       </c>
       <c r="DK14" t="n">
-        <v>0.03163975477218628</v>
+        <v>0</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.01585056446492672</v>
+        <v>0</v>
       </c>
       <c r="DM14" t="n">
-        <v>0.0009383573196828365</v>
+        <v>0</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.006020921748131514</v>
+        <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.002245511393994093</v>
+        <v>0</v>
       </c>
       <c r="DP14" t="n">
-        <v>0.009350565262138844</v>
+        <v>0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.001047934987582266</v>
+        <v>0</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.02416382730007172</v>
+        <v>0</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.005548644345253706</v>
+        <v>0</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.01115523651242256</v>
+        <v>0</v>
       </c>
       <c r="DU14" t="n">
-        <v>0.002063531661406159</v>
+        <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>0.01048941165208817</v>
+        <v>0</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.001823052065446973</v>
+        <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.005860895849764347</v>
+        <v>0</v>
       </c>
       <c r="DY14" t="n">
-        <v>0.01127951312810183</v>
+        <v>0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.01860417239367962</v>
+        <v>0</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.007940707728266716</v>
+        <v>0</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.002128223888576031</v>
+        <v>0</v>
       </c>
       <c r="EC14" t="n">
-        <v>0.01860787905752659</v>
+        <v>0</v>
       </c>
       <c r="ED14" t="n">
-        <v>0.01356907747685909</v>
+        <v>0</v>
       </c>
       <c r="EE14" t="n">
-        <v>0.007173112127929926</v>
+        <v>0</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.01376512832939625</v>
+        <v>0</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.001867660321295261</v>
+        <v>0</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.02390212193131447</v>
+        <v>0</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.01255633402615786</v>
+        <v>0</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.0006256558699533343</v>
+        <v>0</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.01152257435023785</v>
+        <v>0</v>
       </c>
       <c r="EL14" t="n">
-        <v>0.006129790563136339</v>
+        <v>0</v>
       </c>
       <c r="EM14" t="n">
-        <v>0.003883784171193838</v>
+        <v>0</v>
       </c>
       <c r="EN14" t="n">
-        <v>0.005171552300453186</v>
+        <v>0</v>
       </c>
       <c r="EO14" t="n">
-        <v>0.007251205388456583</v>
+        <v>0</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.01381120830774307</v>
+        <v>0</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.01154819875955582</v>
+        <v>0</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.02303285524249077</v>
+        <v>0</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.01432986371219158</v>
+        <v>0</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.02492158301174641</v>
+        <v>0</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.006493133027106524</v>
+        <v>0</v>
       </c>
       <c r="EV14" t="n">
-        <v>0.01307312492281199</v>
+        <v>0</v>
       </c>
       <c r="EW14" t="n">
-        <v>0.006508077960461378</v>
+        <v>0</v>
       </c>
       <c r="EX14" t="n">
-        <v>0.001458185724914074</v>
+        <v>0</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.01220082305371761</v>
+        <v>0</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.01230878848582506</v>
+        <v>0</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.02910514362156391</v>
+        <v>0</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.001155398553237319</v>
+        <v>0</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.007348643615841866</v>
+        <v>0</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.003597251605242491</v>
+        <v>0</v>
       </c>
       <c r="FE14" t="n">
-        <v>0.006317466963082552</v>
+        <v>0</v>
       </c>
       <c r="FF14" t="n">
-        <v>0.009515284560620785</v>
+        <v>0</v>
       </c>
       <c r="FG14" t="n">
-        <v>0.004392152652144432</v>
+        <v>0</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.01826547458767891</v>
+        <v>0</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.001806739601306617</v>
+        <v>0</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.02173664048314095</v>
+        <v>0</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.01776848547160625</v>
+        <v>0</v>
       </c>
       <c r="FL14" t="n">
-        <v>6.659422069787979e-06</v>
+        <v>0</v>
       </c>
       <c r="FM14" t="n">
-        <v>0.01290560234338045</v>
+        <v>0</v>
       </c>
       <c r="FN14" t="n">
-        <v>0.002208945574238896</v>
+        <v>0</v>
       </c>
       <c r="FO14" t="n">
-        <v>0.005839994177222252</v>
+        <v>0</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.01796247065067291</v>
+        <v>0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0.03402476385235786</v>
+        <v>0</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.01419102028012276</v>
+        <v>0</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.02487180940806866</v>
+        <v>0</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.03499484807252884</v>
+        <v>0</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.02010465785861015</v>
+        <v>0</v>
       </c>
       <c r="FV14" t="n">
-        <v>0.00416966388002038</v>
+        <v>0</v>
       </c>
       <c r="FW14" t="n">
-        <v>0.01395518705248833</v>
+        <v>0</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.007110499311238527</v>
+        <v>0</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.003129017073661089</v>
+        <v>0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.008186990395188332</v>
+        <v>0</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.006755432579666376</v>
+        <v>0</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.00248339818790555</v>
+        <v>0</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.04725106060504913</v>
+        <v>0</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.002545625437051058</v>
+        <v>0</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.05060379952192307</v>
+        <v>0</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.002869982738047838</v>
+        <v>0</v>
       </c>
       <c r="GG14" t="n">
-        <v>0.003136326791718602</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>0.001512573915533721</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0.009818813763558865</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.001471070805564523</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.004978022538125515</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.003272096859291196</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.008165049366652966</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.0003354864893481135</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.003621379612013698</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.001211999915540218</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.001875880407169461</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.008050017990171909</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.0008939615800045431</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.002426748629659414</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.0008375872857868671</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.00618719682097435</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0.0001619234681129456</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.0003195884055458009</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.001043901545926929</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.0005440739914774895</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0.0006992191774770617</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0.0002502719289623201</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0.002271959790959954</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0.0019499771296978</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0.001394628081470728</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0.001251553068868816</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0.001677219523116946</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0.0007613071938976645</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0.001148883835412562</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>5.588767817243934e-05</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0.0001931602746481076</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0.001074035535566509</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0.001629144884645939</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0.0005939282709732652</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>9.759666863828897e-05</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0.0003304052515886724</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0.001403283444233239</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0.001199167454615235</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0.001479560392908752</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>0.0008589122444391251</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>0.0003866901388391852</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0.0007260316051542759</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0.001429951516911387</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>9.29835659917444e-05</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0.0009654038003645837</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>0.001197680132463574</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0.000126286904560402</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>0.005294014234095812</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0.001182544627226889</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0.0009898605057969689</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0.0007212539203464985</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>0.004004980903118849</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0.001442227512598038</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>0.001209041103720665</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>0.001973041798919439</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>0.001540734083391726</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>0.0005578628042712808</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>0.001433969009667635</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>0.0001047610276145861</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>0.003205040702596307</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>0.00178367889020592</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>0.001590645406395197</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>0.001461880514398217</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>0.001192134455777705</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>0.0001335022388957441</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>0.00254432437941432</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>0.0008805346442386508</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>0.001012629014439881</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>0.0008809937280602753</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>0.001288204919546843</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>0.0007168205920606852</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>0.0004090607399120927</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>0.0004669141490012407</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>0.0008373711025342345</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>0.004004277288913727</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>0.001553252339363098</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>0.0009053901303559542</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>0.0003500333405099809</v>
-      </c>
-      <c r="BZ15" t="n">
-        <v>0.0009567183442413807</v>
-      </c>
-      <c r="CA15" t="n">
-        <v>0.0002839361550286412</v>
-      </c>
-      <c r="CB15" t="n">
-        <v>0.0004446581879165024</v>
-      </c>
-      <c r="CC15" t="n">
-        <v>0.00160095957107842</v>
-      </c>
-      <c r="CD15" t="n">
-        <v>0.000588041846640408</v>
-      </c>
-      <c r="CE15" t="n">
-        <v>0.0009255282930098474</v>
-      </c>
-      <c r="CF15" t="n">
-        <v>0.0006962819024920464</v>
-      </c>
-      <c r="CG15" t="n">
-        <v>0.001023802789859474</v>
-      </c>
-      <c r="CH15" t="n">
-        <v>0.0001845958031481132</v>
-      </c>
-      <c r="CI15" t="n">
-        <v>0.001436279155313969</v>
-      </c>
-      <c r="CJ15" t="n">
-        <v>0.0008243893971666694</v>
-      </c>
-      <c r="CK15" t="n">
-        <v>0.0007946955738589168</v>
-      </c>
-      <c r="CL15" t="n">
-        <v>0.001040180097334087</v>
-      </c>
-      <c r="CM15" t="n">
-        <v>0.0005655803834088147</v>
-      </c>
-      <c r="CN15" t="n">
-        <v>0.00252455729059875</v>
-      </c>
-      <c r="CO15" t="n">
-        <v>0.0006917231366969645</v>
-      </c>
-      <c r="CP15" t="n">
-        <v>0.001731883850879967</v>
-      </c>
-      <c r="CQ15" t="n">
-        <v>4.304580215830356e-05</v>
-      </c>
-      <c r="CR15" t="n">
-        <v>0.0002830695011653006</v>
-      </c>
-      <c r="CS15" t="n">
-        <v>0.002448670333251357</v>
-      </c>
-      <c r="CT15" t="n">
-        <v>0.002226645825430751</v>
-      </c>
-      <c r="CU15" t="n">
-        <v>0.0001946849224623293</v>
-      </c>
-      <c r="CV15" t="n">
-        <v>0.0003118262393400073</v>
-      </c>
-      <c r="CW15" t="n">
-        <v>0.001180523773655295</v>
-      </c>
-      <c r="CX15" t="n">
-        <v>0.0006030159420333803</v>
-      </c>
-      <c r="CY15" t="n">
-        <v>0.001239941106177866</v>
-      </c>
-      <c r="CZ15" t="n">
-        <v>5.756512837251648e-05</v>
-      </c>
-      <c r="DA15" t="n">
-        <v>0.00195880071260035</v>
-      </c>
-      <c r="DB15" t="n">
-        <v>0.0007135416963137686</v>
-      </c>
-      <c r="DC15" t="n">
-        <v>0.001160160638391972</v>
-      </c>
-      <c r="DD15" t="n">
-        <v>0.0005313438014127314</v>
-      </c>
-      <c r="DE15" t="n">
-        <v>1.607689773663878e-05</v>
-      </c>
-      <c r="DF15" t="n">
-        <v>0.001368124736472964</v>
-      </c>
-      <c r="DG15" t="n">
-        <v>0.001320475712418556</v>
-      </c>
-      <c r="DH15" t="n">
-        <v>0.004170896485447884</v>
-      </c>
-      <c r="DI15" t="n">
-        <v>0.004493166226893663</v>
-      </c>
-      <c r="DJ15" t="n">
-        <v>0.002639617770910263</v>
-      </c>
-      <c r="DK15" t="n">
-        <v>0.001514508854597807</v>
-      </c>
-      <c r="DL15" t="n">
-        <v>0.003361535025760531</v>
-      </c>
-      <c r="DM15" t="n">
-        <v>0.002272812649607658</v>
-      </c>
-      <c r="DN15" t="n">
-        <v>0.0001898249902296811</v>
-      </c>
-      <c r="DO15" t="n">
-        <v>0.0005416242638602853</v>
-      </c>
-      <c r="DP15" t="n">
-        <v>0.0004104478575754911</v>
-      </c>
-      <c r="DQ15" t="n">
-        <v>0.0001920699432957917</v>
-      </c>
-      <c r="DR15" t="n">
-        <v>0.0008824722608551383</v>
-      </c>
-      <c r="DS15" t="n">
-        <v>0.0009539697202853858</v>
-      </c>
-      <c r="DT15" t="n">
-        <v>0.00127281725872308</v>
-      </c>
-      <c r="DU15" t="n">
-        <v>0.00120560301002115</v>
-      </c>
-      <c r="DV15" t="n">
-        <v>0.001594192581251264</v>
-      </c>
-      <c r="DW15" t="n">
-        <v>0.0001281968434341252</v>
-      </c>
-      <c r="DX15" t="n">
-        <v>0.0006558428285643458</v>
-      </c>
-      <c r="DY15" t="n">
-        <v>0.0001167900918517262</v>
-      </c>
-      <c r="DZ15" t="n">
-        <v>0.0002069654874503613</v>
-      </c>
-      <c r="EA15" t="n">
-        <v>8.449226152151823e-05</v>
-      </c>
-      <c r="EB15" t="n">
-        <v>0.0002406883286312222</v>
-      </c>
-      <c r="EC15" t="n">
-        <v>0.0005881891120225191</v>
-      </c>
-      <c r="ED15" t="n">
-        <v>0.0008520839619450271</v>
-      </c>
-      <c r="EE15" t="n">
-        <v>0.0008954693330451846</v>
-      </c>
-      <c r="EF15" t="n">
-        <v>9.011017391458154e-05</v>
-      </c>
-      <c r="EG15" t="n">
-        <v>0.0008966088062152267</v>
-      </c>
-      <c r="EH15" t="n">
-        <v>0.0008185705519281328</v>
-      </c>
-      <c r="EI15" t="n">
-        <v>9.89045511232689e-05</v>
-      </c>
-      <c r="EJ15" t="n">
-        <v>2.286832022946328e-05</v>
-      </c>
-      <c r="EK15" t="n">
-        <v>0.001853534486144781</v>
-      </c>
-      <c r="EL15" t="n">
-        <v>0.000727218110114336</v>
-      </c>
-      <c r="EM15" t="n">
-        <v>0.0005600386648438871</v>
-      </c>
-      <c r="EN15" t="n">
-        <v>0.0005644353805109859</v>
-      </c>
-      <c r="EO15" t="n">
-        <v>0.0006448545027524233</v>
-      </c>
-      <c r="EP15" t="n">
-        <v>0.0003079347079619765</v>
-      </c>
-      <c r="EQ15" t="n">
-        <v>0.0001037330948747694</v>
-      </c>
-      <c r="ER15" t="n">
-        <v>0.001304382691159844</v>
-      </c>
-      <c r="ES15" t="n">
-        <v>0.001280852709896863</v>
-      </c>
-      <c r="ET15" t="n">
-        <v>0.002224184805527329</v>
-      </c>
-      <c r="EU15" t="n">
-        <v>0.0007048262050375342</v>
-      </c>
-      <c r="EV15" t="n">
-        <v>0.003527171909809113</v>
-      </c>
-      <c r="EW15" t="n">
-        <v>0.0005903084529563785</v>
-      </c>
-      <c r="EX15" t="n">
-        <v>0.0001211513881571591</v>
-      </c>
-      <c r="EY15" t="n">
-        <v>0.000723794219084084</v>
-      </c>
-      <c r="EZ15" t="n">
-        <v>0.0004537226923275739</v>
-      </c>
-      <c r="FA15" t="n">
-        <v>0.001336832996457815</v>
-      </c>
-      <c r="FB15" t="n">
-        <v>0.0004099908983334899</v>
-      </c>
-      <c r="FC15" t="n">
-        <v>0.00120110553689301</v>
-      </c>
-      <c r="FD15" t="n">
-        <v>0.001151361502707005</v>
-      </c>
-      <c r="FE15" t="n">
-        <v>0.0007204325520433486</v>
-      </c>
-      <c r="FF15" t="n">
-        <v>0.001153351622633636</v>
-      </c>
-      <c r="FG15" t="n">
-        <v>0.0006818136898800731</v>
-      </c>
-      <c r="FH15" t="n">
-        <v>0.001408741227351129</v>
-      </c>
-      <c r="FI15" t="n">
-        <v>0.0009913458488881588</v>
-      </c>
-      <c r="FJ15" t="n">
-        <v>0.002056581899523735</v>
-      </c>
-      <c r="FK15" t="n">
-        <v>0.0007125341217033565</v>
-      </c>
-      <c r="FL15" t="n">
-        <v>8.825632539810613e-05</v>
-      </c>
-      <c r="FM15" t="n">
-        <v>0.0007828362286090851</v>
-      </c>
-      <c r="FN15" t="n">
-        <v>0.001434574602171779</v>
-      </c>
-      <c r="FO15" t="n">
-        <v>0.0004393545677885413</v>
-      </c>
-      <c r="FP15" t="n">
-        <v>0.0006018226267769933</v>
-      </c>
-      <c r="FQ15" t="n">
-        <v>0.001729653216898441</v>
-      </c>
-      <c r="FR15" t="n">
-        <v>0.001197924604639411</v>
-      </c>
-      <c r="FS15" t="n">
-        <v>0.001482775318436325</v>
-      </c>
-      <c r="FT15" t="n">
-        <v>0.0003519703168421984</v>
-      </c>
-      <c r="FU15" t="n">
-        <v>0.0002612823154777288</v>
-      </c>
-      <c r="FV15" t="n">
-        <v>0.000675405259244144</v>
-      </c>
-      <c r="FW15" t="n">
-        <v>0.0004498636990319937</v>
-      </c>
-      <c r="FX15" t="n">
-        <v>0.0003474969998933375</v>
-      </c>
-      <c r="FY15" t="n">
-        <v>0.001348640536889434</v>
-      </c>
-      <c r="FZ15" t="n">
-        <v>0.001244629034772515</v>
-      </c>
-      <c r="GA15" t="n">
-        <v>0.0006005652248859406</v>
-      </c>
-      <c r="GB15" t="n">
-        <v>0.001237601973116398</v>
-      </c>
-      <c r="GC15" t="n">
-        <v>0.003164137713611126</v>
-      </c>
-      <c r="GD15" t="n">
-        <v>0.0008371652802452445</v>
-      </c>
-      <c r="GE15" t="n">
-        <v>0.005263815633952618</v>
-      </c>
-      <c r="GF15" t="n">
-        <v>0.0002433017798466608</v>
-      </c>
-      <c r="GG15" t="n">
-        <v>0.0003517476725392044</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>0</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="EA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="EB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="EC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="ED16" t="n">
-        <v>0</v>
-      </c>
-      <c r="EE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="EF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="EG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="EH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="EI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="EJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="EK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="EL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="EM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="EN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="EO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="EP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="EQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="ER16" t="n">
-        <v>0</v>
-      </c>
-      <c r="ES16" t="n">
-        <v>0</v>
-      </c>
-      <c r="ET16" t="n">
-        <v>0</v>
-      </c>
-      <c r="EU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="EV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="EW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="EX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="EY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="EZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="FZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="GA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="GB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="GC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="GD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="GE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="GF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="GG16" t="n">
         <v>0</v>
       </c>
     </row>
